--- a/Citizens_Standard_Builder.xlsx
+++ b/Citizens_Standard_Builder.xlsx
@@ -12,8 +12,9 @@
     <sheet name="Projection" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Comparison" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Mode Presets" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="How It Works" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Stress Test" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Mode Presets" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="How It Works" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -332,8 +333,30 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B91" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Stable Floor at horizon under steady equity return + steady CPI assumptions.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="272">
   <si>
     <t xml:space="preserve">Citizens Standard — Interactive Model Builder</t>
   </si>
@@ -826,6 +849,84 @@
     <t xml:space="preserve">Alaska Department of Revenue: PFD historical range $1,200-$3,300/year.</t>
   </si>
   <si>
+    <t xml:space="preserve">Stress Test — Historical Adverse Sequences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What happens to the Stable Floor when a citizen lives through a real historical bad period? Each scenario applies year-by-year actual returns and inflation from a real era. The framework's structural advantage is what survives this stress test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smooth baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great Depression (1929-1944)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1970s Stagflation (1966-1982)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000s Lost Decade (2000-2009)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor (nom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor (real)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headline outputs at horizon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4% withdrawal income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs. smooth baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">× median American</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smooth baseline (no shocks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great Depression (age 25-40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1970s Stagflation (age 30-46)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000s Lost Decade (age 35-44)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources for historical sequences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Shiller's annual real returns dataset (Yale University, 1871-present): http://www.econ.yale.edu/~shiller/data.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLS Consumer Price Index Historical Tables (annual averages, 1913-present)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great Depression sequence (1929-1944): real annualized return ≈ +1.5% with severe year-to-year variation; CPI deflation 1929-1933 then mild inflation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1970s Stagflation sequence (1966-1982): real annualized return ≈ -1.0%; CPI annualized ≈ 7.5% with peaks above 13%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000s Lost Decade sequence (2000-2009): real annualized return ≈ -3.0% (dot-com crash + GFC); CPI annualized ≈ 2.5%</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mode reference values from the paper</t>
   </si>
   <si>
@@ -1073,13 +1174,19 @@
   </si>
   <si>
     <t xml:space="preserve">Side-by-side view of Citizens Standard against 7 alternative systems (Fed status quo, Chicago Plan, Friedman k-rule, Bitcoin, Alaska PFD, UBI, MMT). Adjust the comparison-specific assumptions at the top of that sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stress Test sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year-by-year simulation of the Stable Floor under three real historical adverse sequences (Great Depression 1929-1944, 1970s Stagflation 1966-1982, 2000s Lost Decade 2000-2009) plus the smooth baseline. Returns and CPI for stress periods come from Robert Shiller's dataset and BLS historical CPI. Headline outputs at top show Stable Floor at horizon, 4% withdrawal income, percent change vs. baseline, and the multiple of $87,571 (median American 401k at 55-64). Adjust your equity return and CPI inputs on the Inputs sheet to see how different baseline assumptions change the stress test outcomes.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%;\(0.00%\);\-"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
@@ -1088,8 +1195,12 @@
     <numFmt numFmtId="169" formatCode="0.0000"/>
     <numFmt numFmtId="170" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="171" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="172" formatCode="0.00%;\(0.00%\);\-"/>
+    <numFmt numFmtId="173" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="174" formatCode="0.0\×"/>
+    <numFmt numFmtId="175" formatCode="0.0%;\(0.0%\);\-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1194,8 +1305,16 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFA32D2D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1211,7 +1330,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1EFE8"/>
-        <bgColor rgb="FFE6F1FB"/>
+        <bgColor rgb="FFFCEBEB"/>
       </patternFill>
     </fill>
     <fill>
@@ -1232,8 +1351,14 @@
         <bgColor rgb="FFE6F1FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEBEB"/>
+        <bgColor rgb="FFF1EFE8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1248,6 +1373,19 @@
       <right style="thin">
         <color rgb="FFBFBFBF"/>
       </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
@@ -1282,7 +1420,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="63">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1447,7 +1585,67 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1459,11 +1657,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1471,12 +1665,12 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1525,7 +1719,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFE6F1FB"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFCEBEB"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -7624,6 +7818,6189 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:R102"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="3" style="0" width="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+    </row>
+    <row r="2" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="H6" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="I6" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="J6" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="K6" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="L6" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="M6" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="N6" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="O6" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="P6" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q6" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="R6" s="46" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D7" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="49" t="n">
+        <f aca="false">((Projection!G5/MAX(Projection!F5,1))+Projection!J5)*(1+C7)</f>
+        <v>2629.02412280702</v>
+      </c>
+      <c r="F7" s="49" t="n">
+        <f aca="false">E7/(1+Inputs!B13)^(0+1)</f>
+        <v>2629.02412280702</v>
+      </c>
+      <c r="G7" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H7" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="49" t="n">
+        <f aca="false">((Projection!G5/MAX(Projection!F5,1))+Projection!J5)*(1+G7)</f>
+        <v>2629.02412280702</v>
+      </c>
+      <c r="J7" s="49" t="n">
+        <f aca="false">I7/(1+H7)</f>
+        <v>2629.02412280702</v>
+      </c>
+      <c r="K7" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L7" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="49" t="n">
+        <f aca="false">((Projection!G5/MAX(Projection!F5,1))+Projection!J5)*(1+K7)</f>
+        <v>2629.02412280702</v>
+      </c>
+      <c r="N7" s="49" t="n">
+        <f aca="false">M7/(1+L7)</f>
+        <v>2629.02412280702</v>
+      </c>
+      <c r="O7" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P7" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="49" t="n">
+        <f aca="false">((Projection!G5/MAX(Projection!F5,1))+Projection!J5)*(1+O7)</f>
+        <v>2629.02412280702</v>
+      </c>
+      <c r="R7" s="49" t="n">
+        <f aca="false">Q7/(1+P7)</f>
+        <v>2629.02412280702</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D8" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="49" t="n">
+        <f aca="false">(E7+Projection!J6)*(1+C8)</f>
+        <v>3042.48008068212</v>
+      </c>
+      <c r="F8" s="49" t="n">
+        <f aca="false">E8/(1+Inputs!B13)^(1+1)</f>
+        <v>3042.48008068212</v>
+      </c>
+      <c r="G8" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H8" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="49" t="n">
+        <f aca="false">(I7+Projection!J6)*(1+G8)</f>
+        <v>3042.48008068212</v>
+      </c>
+      <c r="J8" s="49" t="n">
+        <f aca="false">I8/PRODUCT(1+H$7:H8)</f>
+        <v>3042.48008068212</v>
+      </c>
+      <c r="K8" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L8" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="49" t="n">
+        <f aca="false">(M7+Projection!J6)*(1+K8)</f>
+        <v>3042.48008068212</v>
+      </c>
+      <c r="N8" s="49" t="n">
+        <f aca="false">M8/PRODUCT(1+L$7:L8)</f>
+        <v>3042.48008068212</v>
+      </c>
+      <c r="O8" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P8" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="49" t="n">
+        <f aca="false">(Q7+Projection!J6)*(1+O8)</f>
+        <v>3042.48008068212</v>
+      </c>
+      <c r="R8" s="49" t="n">
+        <f aca="false">Q8/PRODUCT(1+P$7:P8)</f>
+        <v>3042.48008068212</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D9" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="49" t="n">
+        <f aca="false">(E8+Projection!J7)*(1+C9)</f>
+        <v>3486.43111447421</v>
+      </c>
+      <c r="F9" s="49" t="n">
+        <f aca="false">E9/(1+Inputs!B13)^(2+1)</f>
+        <v>3486.43111447421</v>
+      </c>
+      <c r="G9" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H9" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="49" t="n">
+        <f aca="false">(I8+Projection!J7)*(1+G9)</f>
+        <v>3486.43111447421</v>
+      </c>
+      <c r="J9" s="49" t="n">
+        <f aca="false">I9/PRODUCT(1+H$7:H9)</f>
+        <v>3486.43111447421</v>
+      </c>
+      <c r="K9" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L9" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="49" t="n">
+        <f aca="false">(M8+Projection!J7)*(1+K9)</f>
+        <v>3486.43111447421</v>
+      </c>
+      <c r="N9" s="49" t="n">
+        <f aca="false">M9/PRODUCT(1+L$7:L9)</f>
+        <v>3486.43111447421</v>
+      </c>
+      <c r="O9" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P9" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="49" t="n">
+        <f aca="false">(Q8+Projection!J7)*(1+O9)</f>
+        <v>3486.43111447421</v>
+      </c>
+      <c r="R9" s="49" t="n">
+        <f aca="false">Q9/PRODUCT(1+P$7:P9)</f>
+        <v>3486.43111447421</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D10" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="49" t="n">
+        <f aca="false">(E9+Projection!J8)*(1+C10)</f>
+        <v>3962.91344051574</v>
+      </c>
+      <c r="F10" s="49" t="n">
+        <f aca="false">E10/(1+Inputs!B13)^(3+1)</f>
+        <v>3962.91344051574</v>
+      </c>
+      <c r="G10" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H10" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="49" t="n">
+        <f aca="false">(I9+Projection!J8)*(1+G10)</f>
+        <v>3962.91344051574</v>
+      </c>
+      <c r="J10" s="49" t="n">
+        <f aca="false">I10/PRODUCT(1+H$7:H10)</f>
+        <v>3962.91344051574</v>
+      </c>
+      <c r="K10" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L10" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="49" t="n">
+        <f aca="false">(M9+Projection!J8)*(1+K10)</f>
+        <v>3962.91344051574</v>
+      </c>
+      <c r="N10" s="49" t="n">
+        <f aca="false">M10/PRODUCT(1+L$7:L10)</f>
+        <v>3962.91344051574</v>
+      </c>
+      <c r="O10" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P10" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="49" t="n">
+        <f aca="false">(Q9+Projection!J8)*(1+O10)</f>
+        <v>3962.91344051574</v>
+      </c>
+      <c r="R10" s="49" t="n">
+        <f aca="false">Q10/PRODUCT(1+P$7:P10)</f>
+        <v>3962.91344051574</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D11" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="49" t="n">
+        <f aca="false">(E10+Projection!J9)*(1+C11)</f>
+        <v>4474.09643571416</v>
+      </c>
+      <c r="F11" s="49" t="n">
+        <f aca="false">E11/(1+Inputs!B13)^(4+1)</f>
+        <v>4474.09643571416</v>
+      </c>
+      <c r="G11" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H11" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="49" t="n">
+        <f aca="false">(I10+Projection!J9)*(1+G11)</f>
+        <v>4474.09643571416</v>
+      </c>
+      <c r="J11" s="49" t="n">
+        <f aca="false">I11/PRODUCT(1+H$7:H11)</f>
+        <v>4474.09643571416</v>
+      </c>
+      <c r="K11" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L11" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="49" t="n">
+        <f aca="false">(M10+Projection!J9)*(1+K11)</f>
+        <v>4474.09643571416</v>
+      </c>
+      <c r="N11" s="49" t="n">
+        <f aca="false">M11/PRODUCT(1+L$7:L11)</f>
+        <v>4474.09643571416</v>
+      </c>
+      <c r="O11" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P11" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="49" t="n">
+        <f aca="false">(Q10+Projection!J9)*(1+O11)</f>
+        <v>4474.09643571416</v>
+      </c>
+      <c r="R11" s="49" t="n">
+        <f aca="false">Q11/PRODUCT(1+P$7:P11)</f>
+        <v>4474.09643571416</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D12" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="49" t="n">
+        <f aca="false">(E11+Projection!J10)*(1+C12)</f>
+        <v>5022.29130502682</v>
+      </c>
+      <c r="F12" s="49" t="n">
+        <f aca="false">E12/(1+Inputs!B13)^(5+1)</f>
+        <v>5022.29130502682</v>
+      </c>
+      <c r="G12" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H12" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="49" t="n">
+        <f aca="false">(I11+Projection!J10)*(1+G12)</f>
+        <v>5022.29130502682</v>
+      </c>
+      <c r="J12" s="49" t="n">
+        <f aca="false">I12/PRODUCT(1+H$7:H12)</f>
+        <v>5022.29130502682</v>
+      </c>
+      <c r="K12" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L12" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="49" t="n">
+        <f aca="false">(M11+Projection!J10)*(1+K12)</f>
+        <v>5022.29130502682</v>
+      </c>
+      <c r="N12" s="49" t="n">
+        <f aca="false">M12/PRODUCT(1+L$7:L12)</f>
+        <v>5022.29130502682</v>
+      </c>
+      <c r="O12" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P12" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="49" t="n">
+        <f aca="false">(Q11+Projection!J10)*(1+O12)</f>
+        <v>5022.29130502682</v>
+      </c>
+      <c r="R12" s="49" t="n">
+        <f aca="false">Q12/PRODUCT(1+P$7:P12)</f>
+        <v>5022.29130502682</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D13" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="49" t="n">
+        <f aca="false">(E12+Projection!J11)*(1+C13)</f>
+        <v>5609.96031250139</v>
+      </c>
+      <c r="F13" s="49" t="n">
+        <f aca="false">E13/(1+Inputs!B13)^(6+1)</f>
+        <v>5609.96031250139</v>
+      </c>
+      <c r="G13" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H13" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="49" t="n">
+        <f aca="false">(I12+Projection!J11)*(1+G13)</f>
+        <v>5609.96031250139</v>
+      </c>
+      <c r="J13" s="49" t="n">
+        <f aca="false">I13/PRODUCT(1+H$7:H13)</f>
+        <v>5609.96031250139</v>
+      </c>
+      <c r="K13" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L13" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="49" t="n">
+        <f aca="false">(M12+Projection!J11)*(1+K13)</f>
+        <v>5609.96031250139</v>
+      </c>
+      <c r="N13" s="49" t="n">
+        <f aca="false">M13/PRODUCT(1+L$7:L13)</f>
+        <v>5609.96031250139</v>
+      </c>
+      <c r="O13" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P13" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="49" t="n">
+        <f aca="false">(Q12+Projection!J11)*(1+O13)</f>
+        <v>5609.96031250139</v>
+      </c>
+      <c r="R13" s="49" t="n">
+        <f aca="false">Q13/PRODUCT(1+P$7:P13)</f>
+        <v>5609.96031250139</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D14" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="49" t="n">
+        <f aca="false">(E13+Projection!J12)*(1+C14)</f>
+        <v>6239.72661251625</v>
+      </c>
+      <c r="F14" s="49" t="n">
+        <f aca="false">E14/(1+Inputs!B13)^(7+1)</f>
+        <v>6239.72661251625</v>
+      </c>
+      <c r="G14" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H14" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="49" t="n">
+        <f aca="false">(I13+Projection!J12)*(1+G14)</f>
+        <v>6239.72661251625</v>
+      </c>
+      <c r="J14" s="49" t="n">
+        <f aca="false">I14/PRODUCT(1+H$7:H14)</f>
+        <v>6239.72661251625</v>
+      </c>
+      <c r="K14" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L14" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="49" t="n">
+        <f aca="false">(M13+Projection!J12)*(1+K14)</f>
+        <v>6239.72661251625</v>
+      </c>
+      <c r="N14" s="49" t="n">
+        <f aca="false">M14/PRODUCT(1+L$7:L14)</f>
+        <v>6239.72661251625</v>
+      </c>
+      <c r="O14" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P14" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="49" t="n">
+        <f aca="false">(Q13+Projection!J12)*(1+O14)</f>
+        <v>6239.72661251625</v>
+      </c>
+      <c r="R14" s="49" t="n">
+        <f aca="false">Q14/PRODUCT(1+P$7:P14)</f>
+        <v>6239.72661251625</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D15" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="49" t="n">
+        <f aca="false">(E14+Projection!J13)*(1+C15)</f>
+        <v>6914.38472023659</v>
+      </c>
+      <c r="F15" s="49" t="n">
+        <f aca="false">E15/(1+Inputs!B13)^(8+1)</f>
+        <v>6914.38472023659</v>
+      </c>
+      <c r="G15" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H15" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="49" t="n">
+        <f aca="false">(I14+Projection!J13)*(1+G15)</f>
+        <v>6914.38472023659</v>
+      </c>
+      <c r="J15" s="49" t="n">
+        <f aca="false">I15/PRODUCT(1+H$7:H15)</f>
+        <v>6914.38472023659</v>
+      </c>
+      <c r="K15" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L15" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="49" t="n">
+        <f aca="false">(M14+Projection!J13)*(1+K15)</f>
+        <v>6914.38472023659</v>
+      </c>
+      <c r="N15" s="49" t="n">
+        <f aca="false">M15/PRODUCT(1+L$7:L15)</f>
+        <v>6914.38472023659</v>
+      </c>
+      <c r="O15" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P15" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="49" t="n">
+        <f aca="false">(Q14+Projection!J13)*(1+O15)</f>
+        <v>6914.38472023659</v>
+      </c>
+      <c r="R15" s="49" t="n">
+        <f aca="false">Q15/PRODUCT(1+P$7:P15)</f>
+        <v>6914.38472023659</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D16" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="49" t="n">
+        <f aca="false">(E15+Projection!J14)*(1+C16)</f>
+        <v>7636.91166283795</v>
+      </c>
+      <c r="F16" s="49" t="n">
+        <f aca="false">E16/(1+Inputs!B13)^(9+1)</f>
+        <v>7636.91166283795</v>
+      </c>
+      <c r="G16" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H16" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="49" t="n">
+        <f aca="false">(I15+Projection!J14)*(1+G16)</f>
+        <v>7636.91166283795</v>
+      </c>
+      <c r="J16" s="49" t="n">
+        <f aca="false">I16/PRODUCT(1+H$7:H16)</f>
+        <v>7636.91166283795</v>
+      </c>
+      <c r="K16" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L16" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="49" t="n">
+        <f aca="false">(M15+Projection!J14)*(1+K16)</f>
+        <v>7636.91166283795</v>
+      </c>
+      <c r="N16" s="49" t="n">
+        <f aca="false">M16/PRODUCT(1+L$7:L16)</f>
+        <v>7636.91166283795</v>
+      </c>
+      <c r="O16" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P16" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="49" t="n">
+        <f aca="false">(Q15+Projection!J14)*(1+O16)</f>
+        <v>7636.91166283795</v>
+      </c>
+      <c r="R16" s="49" t="n">
+        <f aca="false">Q16/PRODUCT(1+P$7:P16)</f>
+        <v>7636.91166283795</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D17" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="49" t="n">
+        <f aca="false">(E16+Projection!J15)*(1+C17)</f>
+        <v>8410.47885574999</v>
+      </c>
+      <c r="F17" s="49" t="n">
+        <f aca="false">E17/(1+Inputs!B13)^(10+1)</f>
+        <v>8410.47885574999</v>
+      </c>
+      <c r="G17" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H17" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="49" t="n">
+        <f aca="false">(I16+Projection!J15)*(1+G17)</f>
+        <v>8410.47885574999</v>
+      </c>
+      <c r="J17" s="49" t="n">
+        <f aca="false">I17/PRODUCT(1+H$7:H17)</f>
+        <v>8410.47885574999</v>
+      </c>
+      <c r="K17" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L17" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="49" t="n">
+        <f aca="false">(M16+Projection!J15)*(1+K17)</f>
+        <v>8410.47885574999</v>
+      </c>
+      <c r="N17" s="49" t="n">
+        <f aca="false">M17/PRODUCT(1+L$7:L17)</f>
+        <v>8410.47885574999</v>
+      </c>
+      <c r="O17" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P17" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="49" t="n">
+        <f aca="false">(Q16+Projection!J15)*(1+O17)</f>
+        <v>8410.47885574999</v>
+      </c>
+      <c r="R17" s="49" t="n">
+        <f aca="false">Q17/PRODUCT(1+P$7:P17)</f>
+        <v>8410.47885574999</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D18" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="49" t="n">
+        <f aca="false">(E17+Projection!J16)*(1+C18)</f>
+        <v>9238.46475104948</v>
+      </c>
+      <c r="F18" s="49" t="n">
+        <f aca="false">E18/(1+Inputs!B13)^(11+1)</f>
+        <v>9238.46475104948</v>
+      </c>
+      <c r="G18" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H18" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="49" t="n">
+        <f aca="false">(I17+Projection!J16)*(1+G18)</f>
+        <v>9238.46475104948</v>
+      </c>
+      <c r="J18" s="49" t="n">
+        <f aca="false">I18/PRODUCT(1+H$7:H18)</f>
+        <v>9238.46475104948</v>
+      </c>
+      <c r="K18" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L18" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="49" t="n">
+        <f aca="false">(M17+Projection!J16)*(1+K18)</f>
+        <v>9238.46475104948</v>
+      </c>
+      <c r="N18" s="49" t="n">
+        <f aca="false">M18/PRODUCT(1+L$7:L18)</f>
+        <v>9238.46475104948</v>
+      </c>
+      <c r="O18" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P18" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="49" t="n">
+        <f aca="false">(Q17+Projection!J16)*(1+O18)</f>
+        <v>9238.46475104948</v>
+      </c>
+      <c r="R18" s="49" t="n">
+        <f aca="false">Q18/PRODUCT(1+P$7:P18)</f>
+        <v>9238.46475104948</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D19" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="49" t="n">
+        <f aca="false">(E18+Projection!J17)*(1+C19)</f>
+        <v>10124.4683081953</v>
+      </c>
+      <c r="F19" s="49" t="n">
+        <f aca="false">E19/(1+Inputs!B13)^(12+1)</f>
+        <v>10124.4683081953</v>
+      </c>
+      <c r="G19" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H19" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="49" t="n">
+        <f aca="false">(I18+Projection!J17)*(1+G19)</f>
+        <v>10124.4683081953</v>
+      </c>
+      <c r="J19" s="49" t="n">
+        <f aca="false">I19/PRODUCT(1+H$7:H19)</f>
+        <v>10124.4683081953</v>
+      </c>
+      <c r="K19" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L19" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="49" t="n">
+        <f aca="false">(M18+Projection!J17)*(1+K19)</f>
+        <v>10124.4683081953</v>
+      </c>
+      <c r="N19" s="49" t="n">
+        <f aca="false">M19/PRODUCT(1+L$7:L19)</f>
+        <v>10124.4683081953</v>
+      </c>
+      <c r="O19" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P19" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="49" t="n">
+        <f aca="false">(Q18+Projection!J17)*(1+O19)</f>
+        <v>10124.4683081953</v>
+      </c>
+      <c r="R19" s="49" t="n">
+        <f aca="false">Q19/PRODUCT(1+P$7:P19)</f>
+        <v>10124.4683081953</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D20" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="49" t="n">
+        <f aca="false">(E19+Projection!J18)*(1+C20)</f>
+        <v>11072.3233405605</v>
+      </c>
+      <c r="F20" s="49" t="n">
+        <f aca="false">E20/(1+Inputs!B13)^(13+1)</f>
+        <v>11072.3233405605</v>
+      </c>
+      <c r="G20" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H20" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="49" t="n">
+        <f aca="false">(I19+Projection!J18)*(1+G20)</f>
+        <v>11072.3233405605</v>
+      </c>
+      <c r="J20" s="49" t="n">
+        <f aca="false">I20/PRODUCT(1+H$7:H20)</f>
+        <v>11072.3233405605</v>
+      </c>
+      <c r="K20" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L20" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="49" t="n">
+        <f aca="false">(M19+Projection!J18)*(1+K20)</f>
+        <v>11072.3233405605</v>
+      </c>
+      <c r="N20" s="49" t="n">
+        <f aca="false">M20/PRODUCT(1+L$7:L20)</f>
+        <v>11072.3233405605</v>
+      </c>
+      <c r="O20" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P20" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="49" t="n">
+        <f aca="false">(Q19+Projection!J18)*(1+O20)</f>
+        <v>11072.3233405605</v>
+      </c>
+      <c r="R20" s="49" t="n">
+        <f aca="false">Q20/PRODUCT(1+P$7:P20)</f>
+        <v>11072.3233405605</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="47" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="47" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D21" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="49" t="n">
+        <f aca="false">(E20+Projection!J19)*(1+C21)</f>
+        <v>12086.1137946911</v>
+      </c>
+      <c r="F21" s="49" t="n">
+        <f aca="false">E21/(1+Inputs!B13)^(14+1)</f>
+        <v>12086.1137946911</v>
+      </c>
+      <c r="G21" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H21" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="49" t="n">
+        <f aca="false">(I20+Projection!J19)*(1+G21)</f>
+        <v>12086.1137946911</v>
+      </c>
+      <c r="J21" s="49" t="n">
+        <f aca="false">I21/PRODUCT(1+H$7:H21)</f>
+        <v>12086.1137946911</v>
+      </c>
+      <c r="K21" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L21" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="49" t="n">
+        <f aca="false">(M20+Projection!J19)*(1+K21)</f>
+        <v>12086.1137946911</v>
+      </c>
+      <c r="N21" s="49" t="n">
+        <f aca="false">M21/PRODUCT(1+L$7:L21)</f>
+        <v>12086.1137946911</v>
+      </c>
+      <c r="O21" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P21" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="49" t="n">
+        <f aca="false">(Q20+Projection!J19)*(1+O21)</f>
+        <v>12086.1137946911</v>
+      </c>
+      <c r="R21" s="49" t="n">
+        <f aca="false">Q21/PRODUCT(1+P$7:P21)</f>
+        <v>12086.1137946911</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="47" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="47" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D22" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="49" t="n">
+        <f aca="false">(E21+Projection!J20)*(1+C22)</f>
+        <v>13170.1900229223</v>
+      </c>
+      <c r="F22" s="49" t="n">
+        <f aca="false">E22/(1+Inputs!B13)^(15+1)</f>
+        <v>13170.1900229223</v>
+      </c>
+      <c r="G22" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H22" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="49" t="n">
+        <f aca="false">(I21+Projection!J20)*(1+G22)</f>
+        <v>13170.1900229223</v>
+      </c>
+      <c r="J22" s="49" t="n">
+        <f aca="false">I22/PRODUCT(1+H$7:H22)</f>
+        <v>13170.1900229223</v>
+      </c>
+      <c r="K22" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L22" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="49" t="n">
+        <f aca="false">(M21+Projection!J20)*(1+K22)</f>
+        <v>13170.1900229223</v>
+      </c>
+      <c r="N22" s="49" t="n">
+        <f aca="false">M22/PRODUCT(1+L$7:L22)</f>
+        <v>13170.1900229223</v>
+      </c>
+      <c r="O22" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P22" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="49" t="n">
+        <f aca="false">(Q21+Projection!J20)*(1+O22)</f>
+        <v>13170.1900229223</v>
+      </c>
+      <c r="R22" s="49" t="n">
+        <f aca="false">Q22/PRODUCT(1+P$7:P22)</f>
+        <v>13170.1900229223</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="47" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="47" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D23" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="49" t="n">
+        <f aca="false">(E22+Projection!J21)*(1+C23)</f>
+        <v>14329.1861139224</v>
+      </c>
+      <c r="F23" s="49" t="n">
+        <f aca="false">E23/(1+Inputs!B13)^(16+1)</f>
+        <v>14329.1861139224</v>
+      </c>
+      <c r="G23" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H23" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="49" t="n">
+        <f aca="false">(I22+Projection!J21)*(1+G23)</f>
+        <v>14329.1861139224</v>
+      </c>
+      <c r="J23" s="49" t="n">
+        <f aca="false">I23/PRODUCT(1+H$7:H23)</f>
+        <v>14329.1861139224</v>
+      </c>
+      <c r="K23" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L23" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="49" t="n">
+        <f aca="false">(M22+Projection!J21)*(1+K23)</f>
+        <v>14329.1861139224</v>
+      </c>
+      <c r="N23" s="49" t="n">
+        <f aca="false">M23/PRODUCT(1+L$7:L23)</f>
+        <v>14329.1861139224</v>
+      </c>
+      <c r="O23" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P23" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="49" t="n">
+        <f aca="false">(Q22+Projection!J21)*(1+O23)</f>
+        <v>14329.1861139224</v>
+      </c>
+      <c r="R23" s="49" t="n">
+        <f aca="false">Q23/PRODUCT(1+P$7:P23)</f>
+        <v>14329.1861139224</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="47" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="47" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D24" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="49" t="n">
+        <f aca="false">(E23+Projection!J22)*(1+C24)</f>
+        <v>15568.0383499346</v>
+      </c>
+      <c r="F24" s="49" t="n">
+        <f aca="false">E24/(1+Inputs!B13)^(17+1)</f>
+        <v>15568.0383499346</v>
+      </c>
+      <c r="G24" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H24" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="49" t="n">
+        <f aca="false">(I23+Projection!J22)*(1+G24)</f>
+        <v>15568.0383499346</v>
+      </c>
+      <c r="J24" s="49" t="n">
+        <f aca="false">I24/PRODUCT(1+H$7:H24)</f>
+        <v>15568.0383499346</v>
+      </c>
+      <c r="K24" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L24" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="49" t="n">
+        <f aca="false">(M23+Projection!J22)*(1+K24)</f>
+        <v>15568.0383499346</v>
+      </c>
+      <c r="N24" s="49" t="n">
+        <f aca="false">M24/PRODUCT(1+L$7:L24)</f>
+        <v>15568.0383499346</v>
+      </c>
+      <c r="O24" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P24" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="49" t="n">
+        <f aca="false">(Q23+Projection!J22)*(1+O24)</f>
+        <v>15568.0383499346</v>
+      </c>
+      <c r="R24" s="49" t="n">
+        <f aca="false">Q24/PRODUCT(1+P$7:P24)</f>
+        <v>15568.0383499346</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="47" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="47" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D25" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="49" t="n">
+        <f aca="false">(E24+Projection!J23)*(1+C25)</f>
+        <v>16892.0048639535</v>
+      </c>
+      <c r="F25" s="49" t="n">
+        <f aca="false">E25/(1+Inputs!B13)^(18+1)</f>
+        <v>16892.0048639535</v>
+      </c>
+      <c r="G25" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H25" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="49" t="n">
+        <f aca="false">(I24+Projection!J23)*(1+G25)</f>
+        <v>16892.0048639535</v>
+      </c>
+      <c r="J25" s="49" t="n">
+        <f aca="false">I25/PRODUCT(1+H$7:H25)</f>
+        <v>16892.0048639535</v>
+      </c>
+      <c r="K25" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L25" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="49" t="n">
+        <f aca="false">(M24+Projection!J23)*(1+K25)</f>
+        <v>16892.0048639535</v>
+      </c>
+      <c r="N25" s="49" t="n">
+        <f aca="false">M25/PRODUCT(1+L$7:L25)</f>
+        <v>16892.0048639535</v>
+      </c>
+      <c r="O25" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P25" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="49" t="n">
+        <f aca="false">(Q24+Projection!J23)*(1+O25)</f>
+        <v>16892.0048639535</v>
+      </c>
+      <c r="R25" s="49" t="n">
+        <f aca="false">Q25/PRODUCT(1+P$7:P25)</f>
+        <v>16892.0048639535</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="47" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="47" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D26" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="49" t="n">
+        <f aca="false">(E25+Projection!J24)*(1+C26)</f>
+        <v>18306.6865748354</v>
+      </c>
+      <c r="F26" s="49" t="n">
+        <f aca="false">E26/(1+Inputs!B13)^(19+1)</f>
+        <v>18306.6865748354</v>
+      </c>
+      <c r="G26" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H26" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="49" t="n">
+        <f aca="false">(I25+Projection!J24)*(1+G26)</f>
+        <v>18306.6865748354</v>
+      </c>
+      <c r="J26" s="49" t="n">
+        <f aca="false">I26/PRODUCT(1+H$7:H26)</f>
+        <v>18306.6865748354</v>
+      </c>
+      <c r="K26" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L26" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="49" t="n">
+        <f aca="false">(M25+Projection!J24)*(1+K26)</f>
+        <v>18306.6865748354</v>
+      </c>
+      <c r="N26" s="49" t="n">
+        <f aca="false">M26/PRODUCT(1+L$7:L26)</f>
+        <v>18306.6865748354</v>
+      </c>
+      <c r="O26" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P26" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="49" t="n">
+        <f aca="false">(Q25+Projection!J24)*(1+O26)</f>
+        <v>18306.6865748354</v>
+      </c>
+      <c r="R26" s="49" t="n">
+        <f aca="false">Q26/PRODUCT(1+P$7:P26)</f>
+        <v>18306.6865748354</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D27" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="49" t="n">
+        <f aca="false">(E26+Projection!J25)*(1+C27)</f>
+        <v>19818.0494834131</v>
+      </c>
+      <c r="F27" s="49" t="n">
+        <f aca="false">E27/(1+Inputs!B13)^(20+1)</f>
+        <v>19818.0494834131</v>
+      </c>
+      <c r="G27" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H27" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="49" t="n">
+        <f aca="false">(I26+Projection!J25)*(1+G27)</f>
+        <v>19818.0494834131</v>
+      </c>
+      <c r="J27" s="49" t="n">
+        <f aca="false">I27/PRODUCT(1+H$7:H27)</f>
+        <v>19818.0494834131</v>
+      </c>
+      <c r="K27" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L27" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="49" t="n">
+        <f aca="false">(M26+Projection!J25)*(1+K27)</f>
+        <v>19818.0494834131</v>
+      </c>
+      <c r="N27" s="49" t="n">
+        <f aca="false">M27/PRODUCT(1+L$7:L27)</f>
+        <v>19818.0494834131</v>
+      </c>
+      <c r="O27" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P27" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="49" t="n">
+        <f aca="false">(Q26+Projection!J25)*(1+O27)</f>
+        <v>19818.0494834131</v>
+      </c>
+      <c r="R27" s="49" t="n">
+        <f aca="false">Q27/PRODUCT(1+P$7:P27)</f>
+        <v>19818.0494834131</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="47" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="47" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D28" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="49" t="n">
+        <f aca="false">(E27+Projection!J26)*(1+C28)</f>
+        <v>21432.4484180814</v>
+      </c>
+      <c r="F28" s="49" t="n">
+        <f aca="false">E28/(1+Inputs!B13)^(21+1)</f>
+        <v>21432.4484180814</v>
+      </c>
+      <c r="G28" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H28" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="49" t="n">
+        <f aca="false">(I27+Projection!J26)*(1+G28)</f>
+        <v>21432.4484180814</v>
+      </c>
+      <c r="J28" s="49" t="n">
+        <f aca="false">I28/PRODUCT(1+H$7:H28)</f>
+        <v>21432.4484180814</v>
+      </c>
+      <c r="K28" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L28" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="49" t="n">
+        <f aca="false">(M27+Projection!J26)*(1+K28)</f>
+        <v>21432.4484180814</v>
+      </c>
+      <c r="N28" s="49" t="n">
+        <f aca="false">M28/PRODUCT(1+L$7:L28)</f>
+        <v>21432.4484180814</v>
+      </c>
+      <c r="O28" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P28" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="49" t="n">
+        <f aca="false">(Q27+Projection!J26)*(1+O28)</f>
+        <v>21432.4484180814</v>
+      </c>
+      <c r="R28" s="49" t="n">
+        <f aca="false">Q28/PRODUCT(1+P$7:P28)</f>
+        <v>21432.4484180814</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="47" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" s="47" t="n">
+        <v>22</v>
+      </c>
+      <c r="C29" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D29" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="49" t="n">
+        <f aca="false">(E28+Projection!J27)*(1+C29)</f>
+        <v>23156.6523240739</v>
+      </c>
+      <c r="F29" s="49" t="n">
+        <f aca="false">E29/(1+Inputs!B13)^(22+1)</f>
+        <v>23156.6523240739</v>
+      </c>
+      <c r="G29" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H29" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="49" t="n">
+        <f aca="false">(I28+Projection!J27)*(1+G29)</f>
+        <v>23156.6523240739</v>
+      </c>
+      <c r="J29" s="49" t="n">
+        <f aca="false">I29/PRODUCT(1+H$7:H29)</f>
+        <v>23156.6523240739</v>
+      </c>
+      <c r="K29" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L29" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="49" t="n">
+        <f aca="false">(M28+Projection!J27)*(1+K29)</f>
+        <v>23156.6523240739</v>
+      </c>
+      <c r="N29" s="49" t="n">
+        <f aca="false">M29/PRODUCT(1+L$7:L29)</f>
+        <v>23156.6523240739</v>
+      </c>
+      <c r="O29" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P29" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="49" t="n">
+        <f aca="false">(Q28+Projection!J27)*(1+O29)</f>
+        <v>23156.6523240739</v>
+      </c>
+      <c r="R29" s="49" t="n">
+        <f aca="false">Q29/PRODUCT(1+P$7:P29)</f>
+        <v>23156.6523240739</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="47" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="47" t="n">
+        <v>23</v>
+      </c>
+      <c r="C30" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D30" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="49" t="n">
+        <f aca="false">(E29+Projection!J28)*(1+C30)</f>
+        <v>24997.8711967742</v>
+      </c>
+      <c r="F30" s="49" t="n">
+        <f aca="false">E30/(1+Inputs!B13)^(23+1)</f>
+        <v>24997.8711967742</v>
+      </c>
+      <c r="G30" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H30" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="49" t="n">
+        <f aca="false">(I29+Projection!J28)*(1+G30)</f>
+        <v>24997.8711967742</v>
+      </c>
+      <c r="J30" s="49" t="n">
+        <f aca="false">I30/PRODUCT(1+H$7:H30)</f>
+        <v>24997.8711967742</v>
+      </c>
+      <c r="K30" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L30" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="49" t="n">
+        <f aca="false">(M29+Projection!J28)*(1+K30)</f>
+        <v>24997.8711967742</v>
+      </c>
+      <c r="N30" s="49" t="n">
+        <f aca="false">M30/PRODUCT(1+L$7:L30)</f>
+        <v>24997.8711967742</v>
+      </c>
+      <c r="O30" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P30" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="49" t="n">
+        <f aca="false">(Q29+Projection!J28)*(1+O30)</f>
+        <v>24997.8711967742</v>
+      </c>
+      <c r="R30" s="49" t="n">
+        <f aca="false">Q30/PRODUCT(1+P$7:P30)</f>
+        <v>24997.8711967742</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="47" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="47" t="n">
+        <v>24</v>
+      </c>
+      <c r="C31" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D31" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="49" t="n">
+        <f aca="false">(E30+Projection!J29)*(1+C31)</f>
+        <v>26963.7847659258</v>
+      </c>
+      <c r="F31" s="49" t="n">
+        <f aca="false">E31/(1+Inputs!B13)^(24+1)</f>
+        <v>26963.7847659258</v>
+      </c>
+      <c r="G31" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H31" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="49" t="n">
+        <f aca="false">(I30+Projection!J29)*(1+G31)</f>
+        <v>26963.7847659258</v>
+      </c>
+      <c r="J31" s="49" t="n">
+        <f aca="false">I31/PRODUCT(1+H$7:H31)</f>
+        <v>26963.7847659258</v>
+      </c>
+      <c r="K31" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L31" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="49" t="n">
+        <f aca="false">(M30+Projection!J29)*(1+K31)</f>
+        <v>26963.7847659258</v>
+      </c>
+      <c r="N31" s="49" t="n">
+        <f aca="false">M31/PRODUCT(1+L$7:L31)</f>
+        <v>26963.7847659258</v>
+      </c>
+      <c r="O31" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P31" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="49" t="n">
+        <f aca="false">(Q30+Projection!J29)*(1+O31)</f>
+        <v>26963.7847659258</v>
+      </c>
+      <c r="R31" s="49" t="n">
+        <f aca="false">Q31/PRODUCT(1+P$7:P31)</f>
+        <v>26963.7847659258</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="47" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="47" t="n">
+        <v>25</v>
+      </c>
+      <c r="C32" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D32" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="49" t="n">
+        <f aca="false">(E31+Projection!J30)*(1+C32)</f>
+        <v>29062.5730445553</v>
+      </c>
+      <c r="F32" s="49" t="n">
+        <f aca="false">E32/(1+Inputs!B13)^(25+1)</f>
+        <v>29062.5730445553</v>
+      </c>
+      <c r="G32" s="50" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="H32" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="49" t="n">
+        <f aca="false">(I31+Projection!J30)*(1+G32)</f>
+        <v>23741.2568532987</v>
+      </c>
+      <c r="J32" s="49" t="n">
+        <f aca="false">I32/PRODUCT(1+H$7:H32)</f>
+        <v>23741.2568532987</v>
+      </c>
+      <c r="K32" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L32" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="49" t="n">
+        <f aca="false">(M31+Projection!J30)*(1+K32)</f>
+        <v>29062.5730445553</v>
+      </c>
+      <c r="N32" s="49" t="n">
+        <f aca="false">M32/PRODUCT(1+L$7:L32)</f>
+        <v>29062.5730445553</v>
+      </c>
+      <c r="O32" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P32" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="49" t="n">
+        <f aca="false">(Q31+Projection!J30)*(1+O32)</f>
+        <v>29062.5730445553</v>
+      </c>
+      <c r="R32" s="49" t="n">
+        <f aca="false">Q32/PRODUCT(1+P$7:P32)</f>
+        <v>29062.5730445553</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="47" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="47" t="n">
+        <v>26</v>
+      </c>
+      <c r="C33" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D33" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="49" t="n">
+        <f aca="false">(E32+Projection!J31)*(1+C33)</f>
+        <v>31302.9488638158</v>
+      </c>
+      <c r="F33" s="49" t="n">
+        <f aca="false">E33/(1+Inputs!B13)^(26+1)</f>
+        <v>31302.9488638158</v>
+      </c>
+      <c r="G33" s="50" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H33" s="50" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="I33" s="49" t="n">
+        <f aca="false">(I32+Projection!J31)*(1+G33)</f>
+        <v>16849.7868395204</v>
+      </c>
+      <c r="J33" s="49" t="n">
+        <f aca="false">I33/PRODUCT(1+H$7:H33)</f>
+        <v>17264.1258601644</v>
+      </c>
+      <c r="K33" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L33" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="49" t="n">
+        <f aca="false">(M32+Projection!J31)*(1+K33)</f>
+        <v>31302.9488638158</v>
+      </c>
+      <c r="N33" s="49" t="n">
+        <f aca="false">M33/PRODUCT(1+L$7:L33)</f>
+        <v>31302.9488638158</v>
+      </c>
+      <c r="O33" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P33" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="49" t="n">
+        <f aca="false">(Q32+Projection!J31)*(1+O33)</f>
+        <v>31302.9488638158</v>
+      </c>
+      <c r="R33" s="49" t="n">
+        <f aca="false">Q33/PRODUCT(1+P$7:P33)</f>
+        <v>31302.9488638158</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="47" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="47" t="n">
+        <v>27</v>
+      </c>
+      <c r="C34" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D34" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="49" t="n">
+        <f aca="false">(E33+Projection!J32)*(1+C34)</f>
+        <v>33694.1925228411</v>
+      </c>
+      <c r="F34" s="49" t="n">
+        <f aca="false">E34/(1+Inputs!B13)^(27+1)</f>
+        <v>33694.1925228411</v>
+      </c>
+      <c r="G34" s="50" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="H34" s="50" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I34" s="49" t="n">
+        <f aca="false">(I33+Projection!J32)*(1+G34)</f>
+        <v>9451.51758857429</v>
+      </c>
+      <c r="J34" s="49" t="n">
+        <f aca="false">I34/PRODUCT(1+H$7:H34)</f>
+        <v>10386.2830643673</v>
+      </c>
+      <c r="K34" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L34" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="49" t="n">
+        <f aca="false">(M33+Projection!J32)*(1+K34)</f>
+        <v>33694.1925228411</v>
+      </c>
+      <c r="N34" s="49" t="n">
+        <f aca="false">M34/PRODUCT(1+L$7:L34)</f>
+        <v>33694.1925228411</v>
+      </c>
+      <c r="O34" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P34" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="49" t="n">
+        <f aca="false">(Q33+Projection!J32)*(1+O34)</f>
+        <v>33694.1925228411</v>
+      </c>
+      <c r="R34" s="49" t="n">
+        <f aca="false">Q34/PRODUCT(1+P$7:P34)</f>
+        <v>33694.1925228411</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="47" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="47" t="n">
+        <v>28</v>
+      </c>
+      <c r="C35" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D35" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="49" t="n">
+        <f aca="false">(E34+Projection!J33)*(1+C35)</f>
+        <v>36246.1886910893</v>
+      </c>
+      <c r="F35" s="49" t="n">
+        <f aca="false">E35/(1+Inputs!B13)^(28+1)</f>
+        <v>36246.1886910893</v>
+      </c>
+      <c r="G35" s="50" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H35" s="50" t="n">
+        <v>-0.099</v>
+      </c>
+      <c r="I35" s="49" t="n">
+        <f aca="false">(I34+Projection!J33)*(1+G35)</f>
+        <v>8812.1745516297</v>
+      </c>
+      <c r="J35" s="49" t="n">
+        <f aca="false">I35/PRODUCT(1+H$7:H35)</f>
+        <v>9780.43790413951</v>
+      </c>
+      <c r="K35" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L35" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="49" t="n">
+        <f aca="false">(M34+Projection!J33)*(1+K35)</f>
+        <v>36246.1886910893</v>
+      </c>
+      <c r="N35" s="49" t="n">
+        <f aca="false">M35/PRODUCT(1+L$7:L35)</f>
+        <v>36246.1886910893</v>
+      </c>
+      <c r="O35" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P35" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="49" t="n">
+        <f aca="false">(Q34+Projection!J33)*(1+O35)</f>
+        <v>36246.1886910893</v>
+      </c>
+      <c r="R35" s="49" t="n">
+        <f aca="false">Q35/PRODUCT(1+P$7:P35)</f>
+        <v>36246.1886910893</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="47" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" s="47" t="n">
+        <v>29</v>
+      </c>
+      <c r="C36" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D36" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="49" t="n">
+        <f aca="false">(E35+Projection!J34)*(1+C36)</f>
+        <v>38969.465709591</v>
+      </c>
+      <c r="F36" s="49" t="n">
+        <f aca="false">E36/(1+Inputs!B13)^(29+1)</f>
+        <v>38969.465709591</v>
+      </c>
+      <c r="G36" s="50" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H36" s="50" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I36" s="49" t="n">
+        <f aca="false">(I35+Projection!J34)*(1+G36)</f>
+        <v>14193.4018865287</v>
+      </c>
+      <c r="J36" s="49" t="n">
+        <f aca="false">I36/PRODUCT(1+H$7:H36)</f>
+        <v>14080.7558398103</v>
+      </c>
+      <c r="K36" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L36" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="49" t="n">
+        <f aca="false">(M35+Projection!J34)*(1+K36)</f>
+        <v>38969.465709591</v>
+      </c>
+      <c r="N36" s="49" t="n">
+        <f aca="false">M36/PRODUCT(1+L$7:L36)</f>
+        <v>38969.465709591</v>
+      </c>
+      <c r="O36" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P36" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="49" t="n">
+        <f aca="false">(Q35+Projection!J34)*(1+O36)</f>
+        <v>38969.465709591</v>
+      </c>
+      <c r="R36" s="49" t="n">
+        <f aca="false">Q36/PRODUCT(1+P$7:P36)</f>
+        <v>38969.465709591</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="C37" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D37" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="49" t="n">
+        <f aca="false">(E36+Projection!J35)*(1+C37)</f>
+        <v>41875.2374470354</v>
+      </c>
+      <c r="F37" s="49" t="n">
+        <f aca="false">E37/(1+Inputs!B13)^(30+1)</f>
+        <v>41875.2374470354</v>
+      </c>
+      <c r="G37" s="50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H37" s="50" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I37" s="49" t="n">
+        <f aca="false">(I36+Projection!J35)*(1+G37)</f>
+        <v>14252.5397990277</v>
+      </c>
+      <c r="J37" s="49" t="n">
+        <f aca="false">I37/PRODUCT(1+H$7:H37)</f>
+        <v>14055.7591706388</v>
+      </c>
+      <c r="K37" s="50" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L37" s="50" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="M37" s="49" t="n">
+        <f aca="false">(M36+Projection!J35)*(1+K37)</f>
+        <v>35387.5246031285</v>
+      </c>
+      <c r="N37" s="49" t="n">
+        <f aca="false">M37/PRODUCT(1+L$7:L37)</f>
+        <v>34390.2085550325</v>
+      </c>
+      <c r="O37" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P37" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="49" t="n">
+        <f aca="false">(Q36+Projection!J35)*(1+O37)</f>
+        <v>41875.2374470354</v>
+      </c>
+      <c r="R37" s="49" t="n">
+        <f aca="false">Q37/PRODUCT(1+P$7:P37)</f>
+        <v>41875.2374470354</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="47" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" s="47" t="n">
+        <v>31</v>
+      </c>
+      <c r="C38" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D38" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="49" t="n">
+        <f aca="false">(E37+Projection!J36)*(1+C38)</f>
+        <v>44975.4478767616</v>
+      </c>
+      <c r="F38" s="49" t="n">
+        <f aca="false">E38/(1+Inputs!B13)^(31+1)</f>
+        <v>44975.4478767616</v>
+      </c>
+      <c r="G38" s="50" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H38" s="50" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I38" s="49" t="n">
+        <f aca="false">(I37+Projection!J36)*(1+G38)</f>
+        <v>21327.3439691877</v>
+      </c>
+      <c r="J38" s="49" t="n">
+        <f aca="false">I38/PRODUCT(1+H$7:H38)</f>
+        <v>20726.2817970726</v>
+      </c>
+      <c r="K38" s="50" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L38" s="50" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M38" s="49" t="n">
+        <f aca="false">(M37+Projection!J36)*(1+K38)</f>
+        <v>44321.0157610526</v>
+      </c>
+      <c r="N38" s="49" t="n">
+        <f aca="false">M38/PRODUCT(1+L$7:L38)</f>
+        <v>42988.3761018939</v>
+      </c>
+      <c r="O38" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P38" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="49" t="n">
+        <f aca="false">(Q37+Projection!J36)*(1+O38)</f>
+        <v>44975.4478767616</v>
+      </c>
+      <c r="R38" s="49" t="n">
+        <f aca="false">Q38/PRODUCT(1+P$7:P38)</f>
+        <v>44975.4478767616</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="47" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" s="47" t="n">
+        <v>32</v>
+      </c>
+      <c r="C39" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D39" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="49" t="n">
+        <f aca="false">(E38+Projection!J37)*(1+C39)</f>
+        <v>48282.8185515197</v>
+      </c>
+      <c r="F39" s="49" t="n">
+        <f aca="false">E39/(1+Inputs!B13)^(32+1)</f>
+        <v>48282.8185515197</v>
+      </c>
+      <c r="G39" s="50" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H39" s="50" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I39" s="49" t="n">
+        <f aca="false">(I38+Projection!J37)*(1+G39)</f>
+        <v>28627.9962579705</v>
+      </c>
+      <c r="J39" s="49" t="n">
+        <f aca="false">I39/PRODUCT(1+H$7:H39)</f>
+        <v>28288.5338517495</v>
+      </c>
+      <c r="K39" s="50" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L39" s="50" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="M39" s="49" t="n">
+        <f aca="false">(M38+Projection!J37)*(1+K39)</f>
+        <v>49596.5179968088</v>
+      </c>
+      <c r="N39" s="49" t="n">
+        <f aca="false">M39/PRODUCT(1+L$7:L39)</f>
+        <v>47506.2432919625</v>
+      </c>
+      <c r="O39" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P39" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="49" t="n">
+        <f aca="false">(Q38+Projection!J37)*(1+O39)</f>
+        <v>48282.8185515197</v>
+      </c>
+      <c r="R39" s="49" t="n">
+        <f aca="false">Q39/PRODUCT(1+P$7:P39)</f>
+        <v>48282.8185515197</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="47" t="n">
+        <v>33</v>
+      </c>
+      <c r="B40" s="47" t="n">
+        <v>33</v>
+      </c>
+      <c r="C40" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D40" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="49" t="n">
+        <f aca="false">(E39+Projection!J38)*(1+C40)</f>
+        <v>51810.8991643574</v>
+      </c>
+      <c r="F40" s="49" t="n">
+        <f aca="false">E40/(1+Inputs!B13)^(33+1)</f>
+        <v>51810.8991643574</v>
+      </c>
+      <c r="G40" s="50" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="H40" s="50" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I40" s="49" t="n">
+        <f aca="false">(I39+Projection!J38)*(1+G40)</f>
+        <v>18556.1019623527</v>
+      </c>
+      <c r="J40" s="49" t="n">
+        <f aca="false">I40/PRODUCT(1+H$7:H40)</f>
+        <v>18033.1408769219</v>
+      </c>
+      <c r="K40" s="50" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L40" s="50" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="M40" s="49" t="n">
+        <f aca="false">(M39+Projection!J38)*(1+K40)</f>
+        <v>45965.4365706132</v>
+      </c>
+      <c r="N40" s="49" t="n">
+        <f aca="false">M40/PRODUCT(1+L$7:L40)</f>
+        <v>43610.4711296141</v>
+      </c>
+      <c r="O40" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P40" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="49" t="n">
+        <f aca="false">(Q39+Projection!J38)*(1+O40)</f>
+        <v>51810.8991643574</v>
+      </c>
+      <c r="R40" s="49" t="n">
+        <f aca="false">Q40/PRODUCT(1+P$7:P40)</f>
+        <v>51810.8991643574</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="47" t="n">
+        <v>34</v>
+      </c>
+      <c r="B41" s="47" t="n">
+        <v>34</v>
+      </c>
+      <c r="C41" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D41" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="49" t="n">
+        <f aca="false">(E40+Projection!J39)*(1+C41)</f>
+        <v>55574.1213962383</v>
+      </c>
+      <c r="F41" s="49" t="n">
+        <f aca="false">E41/(1+Inputs!B13)^(34+1)</f>
+        <v>55574.1213962383</v>
+      </c>
+      <c r="G41" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H41" s="50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I41" s="49" t="n">
+        <f aca="false">(I40+Projection!J39)*(1+G41)</f>
+        <v>24605.7193323327</v>
+      </c>
+      <c r="J41" s="49" t="n">
+        <f aca="false">I41/PRODUCT(1+H$7:H41)</f>
+        <v>25107.8768697273</v>
+      </c>
+      <c r="K41" s="50" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L41" s="50" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="M41" s="49" t="n">
+        <f aca="false">(M40+Projection!J39)*(1+K41)</f>
+        <v>48190.2834584572</v>
+      </c>
+      <c r="N41" s="49" t="n">
+        <f aca="false">M41/PRODUCT(1+L$7:L41)</f>
+        <v>45548.4720779368</v>
+      </c>
+      <c r="O41" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P41" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="49" t="n">
+        <f aca="false">(Q40+Projection!J39)*(1+O41)</f>
+        <v>55574.1213962383</v>
+      </c>
+      <c r="R41" s="49" t="n">
+        <f aca="false">Q41/PRODUCT(1+P$7:P41)</f>
+        <v>55574.1213962383</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="47" t="n">
+        <v>35</v>
+      </c>
+      <c r="B42" s="47" t="n">
+        <v>35</v>
+      </c>
+      <c r="C42" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D42" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="49" t="n">
+        <f aca="false">(E41+Projection!J40)*(1+C42)</f>
+        <v>59587.8562640303</v>
+      </c>
+      <c r="F42" s="49" t="n">
+        <f aca="false">E42/(1+Inputs!B13)^(35+1)</f>
+        <v>59587.8562640303</v>
+      </c>
+      <c r="G42" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="50" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I42" s="49" t="n">
+        <f aca="false">(I41+Projection!J40)*(1+G42)</f>
+        <v>24982.6366816628</v>
+      </c>
+      <c r="J42" s="49" t="n">
+        <f aca="false">I42/PRODUCT(1+H$7:H42)</f>
+        <v>25108.1775695103</v>
+      </c>
+      <c r="K42" s="50" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L42" s="50" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="M42" s="49" t="n">
+        <f aca="false">(M41+Projection!J40)*(1+K42)</f>
+        <v>55366.6089208774</v>
+      </c>
+      <c r="N42" s="49" t="n">
+        <f aca="false">M42/PRODUCT(1+L$7:L42)</f>
+        <v>53083.9970478211</v>
+      </c>
+      <c r="O42" s="50" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="P42" s="50" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="Q42" s="49" t="n">
+        <f aca="false">(Q41+Projection!J40)*(1+O42)</f>
+        <v>50915.4452584672</v>
+      </c>
+      <c r="R42" s="49" t="n">
+        <f aca="false">Q42/PRODUCT(1+P$7:P42)</f>
+        <v>49241.2429965834</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="47" t="n">
+        <v>36</v>
+      </c>
+      <c r="B43" s="47" t="n">
+        <v>36</v>
+      </c>
+      <c r="C43" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D43" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="49" t="n">
+        <f aca="false">(E42+Projection!J41)*(1+C43)</f>
+        <v>63868.4751963935</v>
+      </c>
+      <c r="F43" s="49" t="n">
+        <f aca="false">E43/(1+Inputs!B13)^(36+1)</f>
+        <v>63868.4751963935</v>
+      </c>
+      <c r="G43" s="50" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H43" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I43" s="49" t="n">
+        <f aca="false">(I42+Projection!J41)*(1+G43)</f>
+        <v>22828.6616967651</v>
+      </c>
+      <c r="J43" s="49" t="n">
+        <f aca="false">I43/PRODUCT(1+H$7:H43)</f>
+        <v>22602.6353433318</v>
+      </c>
+      <c r="K43" s="50" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="L43" s="50" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="M43" s="49" t="n">
+        <f aca="false">(M42+Projection!J41)*(1+K43)</f>
+        <v>66341.4907637216</v>
+      </c>
+      <c r="N43" s="49" t="n">
+        <f aca="false">M43/PRODUCT(1+L$7:L43)</f>
+        <v>64222.1595002145</v>
+      </c>
+      <c r="O43" s="50" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="P43" s="50" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="Q43" s="49" t="n">
+        <f aca="false">(Q42+Projection!J41)*(1+O43)</f>
+        <v>45142.2296510916</v>
+      </c>
+      <c r="R43" s="49" t="n">
+        <f aca="false">Q43/PRODUCT(1+P$7:P43)</f>
+        <v>43912.6747578712</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="47" t="n">
+        <v>37</v>
+      </c>
+      <c r="B44" s="47" t="n">
+        <v>37</v>
+      </c>
+      <c r="C44" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D44" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="49" t="n">
+        <f aca="false">(E43+Projection!J42)*(1+C44)</f>
+        <v>68433.4150798857</v>
+      </c>
+      <c r="F44" s="49" t="n">
+        <f aca="false">E44/(1+Inputs!B13)^(37+1)</f>
+        <v>68433.4150798857</v>
+      </c>
+      <c r="G44" s="50" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="H44" s="50" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="I44" s="49" t="n">
+        <f aca="false">(I43+Projection!J42)*(1+G44)</f>
+        <v>20198.7154191736</v>
+      </c>
+      <c r="J44" s="49" t="n">
+        <f aca="false">I44/PRODUCT(1+H$7:H44)</f>
+        <v>18412.6849764573</v>
+      </c>
+      <c r="K44" s="50" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="L44" s="50" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="M44" s="49" t="n">
+        <f aca="false">(M43+Projection!J42)*(1+K44)</f>
+        <v>56720.2818405883</v>
+      </c>
+      <c r="N44" s="49" t="n">
+        <f aca="false">M44/PRODUCT(1+L$7:L44)</f>
+        <v>53408.9282868063</v>
+      </c>
+      <c r="O44" s="50" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="P44" s="50" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="Q44" s="49" t="n">
+        <f aca="false">(Q43+Projection!J42)*(1+O44)</f>
+        <v>35513.7761388062</v>
+      </c>
+      <c r="R44" s="49" t="n">
+        <f aca="false">Q44/PRODUCT(1+P$7:P44)</f>
+        <v>34954.5040736281</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="47" t="n">
+        <v>38</v>
+      </c>
+      <c r="B45" s="47" t="n">
+        <v>38</v>
+      </c>
+      <c r="C45" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D45" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="49" t="n">
+        <f aca="false">(E44+Projection!J43)*(1+C45)</f>
+        <v>73301.2475333531</v>
+      </c>
+      <c r="F45" s="49" t="n">
+        <f aca="false">E45/(1+Inputs!B13)^(38+1)</f>
+        <v>73301.2475333531</v>
+      </c>
+      <c r="G45" s="50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H45" s="50" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="I45" s="49" t="n">
+        <f aca="false">(I44+Projection!J43)*(1+G45)</f>
+        <v>24711.3153743039</v>
+      </c>
+      <c r="J45" s="49" t="n">
+        <f aca="false">I45/PRODUCT(1+H$7:H45)</f>
+        <v>22629.4096834285</v>
+      </c>
+      <c r="K45" s="50" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="L45" s="50" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M45" s="49" t="n">
+        <f aca="false">(M44+Projection!J43)*(1+K45)</f>
+        <v>41693.4603403343</v>
+      </c>
+      <c r="N45" s="49" t="n">
+        <f aca="false">M45/PRODUCT(1+L$7:L45)</f>
+        <v>37561.6759822831</v>
+      </c>
+      <c r="O45" s="50" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P45" s="50" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="Q45" s="49" t="n">
+        <f aca="false">(Q44+Projection!J43)*(1+O45)</f>
+        <v>46321.0923557027</v>
+      </c>
+      <c r="R45" s="49" t="n">
+        <f aca="false">Q45/PRODUCT(1+P$7:P45)</f>
+        <v>45279.6601717524</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="47" t="n">
+        <v>39</v>
+      </c>
+      <c r="B46" s="47" t="n">
+        <v>39</v>
+      </c>
+      <c r="C46" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D46" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="49" t="n">
+        <f aca="false">(E45+Projection!J44)*(1+C46)</f>
+        <v>78491.7526854492</v>
+      </c>
+      <c r="F46" s="49" t="n">
+        <f aca="false">E46/(1+Inputs!B13)^(39+1)</f>
+        <v>78491.7526854492</v>
+      </c>
+      <c r="G46" s="50" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H46" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I46" s="49" t="n">
+        <f aca="false">(I45+Projection!J44)*(1+G46)</f>
+        <v>31640.1675299886</v>
+      </c>
+      <c r="J46" s="49" t="n">
+        <f aca="false">I46/PRODUCT(1+H$7:H46)</f>
+        <v>30718.6092524161</v>
+      </c>
+      <c r="K46" s="50" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L46" s="50" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="M46" s="49" t="n">
+        <f aca="false">(M45+Projection!J44)*(1+K46)</f>
+        <v>57667.9429813063</v>
+      </c>
+      <c r="N46" s="49" t="n">
+        <f aca="false">M46/PRODUCT(1+L$7:L46)</f>
+        <v>52857.8762431772</v>
+      </c>
+      <c r="O46" s="50" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="P46" s="50" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q46" s="49" t="n">
+        <f aca="false">(Q45+Projection!J44)*(1+O46)</f>
+        <v>51860.3333686283</v>
+      </c>
+      <c r="R46" s="49" t="n">
+        <f aca="false">Q46/PRODUCT(1+P$7:P46)</f>
+        <v>50496.9166198912</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="47" t="n">
+        <v>40</v>
+      </c>
+      <c r="B47" s="47" t="n">
+        <v>40</v>
+      </c>
+      <c r="C47" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D47" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="49" t="n">
+        <f aca="false">(E46+Projection!J45)*(1+C47)</f>
+        <v>84025.9977479901</v>
+      </c>
+      <c r="F47" s="49" t="n">
+        <f aca="false">E47/(1+Inputs!B13)^(40+1)</f>
+        <v>84025.9977479901</v>
+      </c>
+      <c r="G47" s="50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H47" s="50" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="I47" s="49" t="n">
+        <f aca="false">(I46+Projection!J45)*(1+G47)</f>
+        <v>38455.2783745629</v>
+      </c>
+      <c r="J47" s="49" t="n">
+        <f aca="false">I47/PRODUCT(1+H$7:H47)</f>
+        <v>37738.2515942717</v>
+      </c>
+      <c r="K47" s="50" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L47" s="50" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="M47" s="49" t="n">
+        <f aca="false">(M46+Projection!J45)*(1+K47)</f>
+        <v>72011.5625466824</v>
+      </c>
+      <c r="N47" s="49" t="n">
+        <f aca="false">M47/PRODUCT(1+L$7:L47)</f>
+        <v>68063.8587397754</v>
+      </c>
+      <c r="O47" s="50" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P47" s="50" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="Q47" s="49" t="n">
+        <f aca="false">(Q46+Projection!J45)*(1+O47)</f>
+        <v>54879.5427083143</v>
+      </c>
+      <c r="R47" s="49" t="n">
+        <f aca="false">Q47/PRODUCT(1+P$7:P47)</f>
+        <v>53074.9929480796</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="47" t="n">
+        <v>41</v>
+      </c>
+      <c r="B48" s="47" t="n">
+        <v>41</v>
+      </c>
+      <c r="C48" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D48" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="49" t="n">
+        <f aca="false">(E47+Projection!J46)*(1+C48)</f>
+        <v>89926.4206968796</v>
+      </c>
+      <c r="F48" s="49" t="n">
+        <f aca="false">E48/(1+Inputs!B13)^(41+1)</f>
+        <v>89926.4206968796</v>
+      </c>
+      <c r="G48" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H48" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="49" t="n">
+        <f aca="false">(I47+Projection!J46)*(1+G48)</f>
+        <v>41393.6045641796</v>
+      </c>
+      <c r="J48" s="49" t="n">
+        <f aca="false">I48/PRODUCT(1+H$7:H48)</f>
+        <v>41393.6045641796</v>
+      </c>
+      <c r="K48" s="50" t="n">
+        <v>-0.07</v>
+      </c>
+      <c r="L48" s="50" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="M48" s="49" t="n">
+        <f aca="false">(M47+Projection!J46)*(1+K48)</f>
+        <v>67353.8722093547</v>
+      </c>
+      <c r="N48" s="49" t="n">
+        <f aca="false">M48/PRODUCT(1+L$7:L48)</f>
+        <v>63243.0724970467</v>
+      </c>
+      <c r="O48" s="50" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P48" s="50" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="Q48" s="49" t="n">
+        <f aca="false">(Q47+Projection!J46)*(1+O48)</f>
+        <v>64138.1384529247</v>
+      </c>
+      <c r="R48" s="49" t="n">
+        <f aca="false">Q48/PRODUCT(1+P$7:P48)</f>
+        <v>62149.3589660123</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B49" s="47" t="n">
+        <v>42</v>
+      </c>
+      <c r="C49" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D49" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="49" t="n">
+        <f aca="false">(E48+Projection!J47)*(1+C49)</f>
+        <v>96216.9193926002</v>
+      </c>
+      <c r="F49" s="49" t="n">
+        <f aca="false">E49/(1+Inputs!B13)^(42+1)</f>
+        <v>96216.9193926002</v>
+      </c>
+      <c r="G49" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H49" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="49" t="n">
+        <f aca="false">(I48+Projection!J47)*(1+G49)</f>
+        <v>44529.4702112747</v>
+      </c>
+      <c r="J49" s="49" t="n">
+        <f aca="false">I49/PRODUCT(1+H$7:H49)</f>
+        <v>44529.4702112747</v>
+      </c>
+      <c r="K49" s="50" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="L49" s="50" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="M49" s="49" t="n">
+        <f aca="false">(M48+Projection!J47)*(1+K49)</f>
+        <v>72516.015137205</v>
+      </c>
+      <c r="N49" s="49" t="n">
+        <f aca="false">M49/PRODUCT(1+L$7:L49)</f>
+        <v>67394.066112644</v>
+      </c>
+      <c r="O49" s="50" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P49" s="50" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="Q49" s="49" t="n">
+        <f aca="false">(Q48+Projection!J47)*(1+O49)</f>
+        <v>67784.0551576786</v>
+      </c>
+      <c r="R49" s="49" t="n">
+        <f aca="false">Q49/PRODUCT(1+P$7:P49)</f>
+        <v>65937.7968459908</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="47" t="n">
+        <v>43</v>
+      </c>
+      <c r="B50" s="47" t="n">
+        <v>43</v>
+      </c>
+      <c r="C50" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D50" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="49" t="n">
+        <f aca="false">(E49+Projection!J48)*(1+C50)</f>
+        <v>102922.946493847</v>
+      </c>
+      <c r="F50" s="49" t="n">
+        <f aca="false">E50/(1+Inputs!B13)^(43+1)</f>
+        <v>102922.946493847</v>
+      </c>
+      <c r="G50" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H50" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I50" s="49" t="n">
+        <f aca="false">(I49+Projection!J48)*(1+G50)</f>
+        <v>47875.8131157359</v>
+      </c>
+      <c r="J50" s="49" t="n">
+        <f aca="false">I50/PRODUCT(1+H$7:H50)</f>
+        <v>47875.8131157359</v>
+      </c>
+      <c r="K50" s="50" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L50" s="50" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="M50" s="49" t="n">
+        <f aca="false">(M49+Projection!J48)*(1+K50)</f>
+        <v>86069.6248685303</v>
+      </c>
+      <c r="N50" s="49" t="n">
+        <f aca="false">M50/PRODUCT(1+L$7:L50)</f>
+        <v>77261.7817491296</v>
+      </c>
+      <c r="O50" s="50" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="P50" s="50" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="Q50" s="49" t="n">
+        <f aca="false">(Q49+Projection!J48)*(1+O50)</f>
+        <v>42971.2920494866</v>
+      </c>
+      <c r="R50" s="49" t="n">
+        <f aca="false">Q50/PRODUCT(1+P$7:P50)</f>
+        <v>41398.1618973859</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="47" t="n">
+        <v>44</v>
+      </c>
+      <c r="B51" s="47" t="n">
+        <v>44</v>
+      </c>
+      <c r="C51" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D51" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="49" t="n">
+        <f aca="false">(E50+Projection!J49)*(1+C51)</f>
+        <v>110071.610540866</v>
+      </c>
+      <c r="F51" s="49" t="n">
+        <f aca="false">E51/(1+Inputs!B13)^(44+1)</f>
+        <v>110071.610540866</v>
+      </c>
+      <c r="G51" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H51" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="49" t="n">
+        <f aca="false">(I50+Projection!J49)*(1+G51)</f>
+        <v>51446.4134931769</v>
+      </c>
+      <c r="J51" s="49" t="n">
+        <f aca="false">I51/PRODUCT(1+H$7:H51)</f>
+        <v>51446.4134931769</v>
+      </c>
+      <c r="K51" s="50" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L51" s="50" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="M51" s="49" t="n">
+        <f aca="false">(M50+Projection!J49)*(1+K51)</f>
+        <v>114180.400350302</v>
+      </c>
+      <c r="N51" s="49" t="n">
+        <f aca="false">M51/PRODUCT(1+L$7:L51)</f>
+        <v>100599.471674275</v>
+      </c>
+      <c r="O51" s="50" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P51" s="50" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="Q51" s="49" t="n">
+        <f aca="false">(Q50+Projection!J49)*(1+O51)</f>
+        <v>54686.4828005662</v>
+      </c>
+      <c r="R51" s="49" t="n">
+        <f aca="false">Q51/PRODUCT(1+P$7:P51)</f>
+        <v>54906.1072294842</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B52" s="47" t="n">
+        <v>45</v>
+      </c>
+      <c r="C52" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D52" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="49" t="n">
+        <f aca="false">(E51+Projection!J50)*(1+C52)</f>
+        <v>117691.783609521</v>
+      </c>
+      <c r="F52" s="49" t="n">
+        <f aca="false">E52/(1+Inputs!B13)^(45+1)</f>
+        <v>117691.783609521</v>
+      </c>
+      <c r="G52" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H52" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I52" s="49" t="n">
+        <f aca="false">(I51+Projection!J50)*(1+G52)</f>
+        <v>55255.9487537325</v>
+      </c>
+      <c r="J52" s="49" t="n">
+        <f aca="false">I52/PRODUCT(1+H$7:H52)</f>
+        <v>55255.9487537325</v>
+      </c>
+      <c r="K52" s="50" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L52" s="50" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="M52" s="49" t="n">
+        <f aca="false">(M51+Projection!J50)*(1+K52)</f>
+        <v>108886.631472998</v>
+      </c>
+      <c r="N52" s="49" t="n">
+        <f aca="false">M52/PRODUCT(1+L$7:L52)</f>
+        <v>98718.6142094268</v>
+      </c>
+      <c r="O52" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P52" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q52" s="49" t="n">
+        <f aca="false">(Q51+Projection!J50)*(1+O52)</f>
+        <v>58706.6225661022</v>
+      </c>
+      <c r="R52" s="49" t="n">
+        <f aca="false">Q52/PRODUCT(1+P$7:P52)</f>
+        <v>58706.6225661022</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B53" s="47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C53" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D53" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="49" t="n">
+        <f aca="false">(E52+Projection!J51)*(1+C53)</f>
+        <v>125814.215963214</v>
+      </c>
+      <c r="F53" s="49" t="n">
+        <f aca="false">E53/(1+Inputs!B13)^(46+1)</f>
+        <v>125814.215963214</v>
+      </c>
+      <c r="G53" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H53" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="49" t="n">
+        <f aca="false">(I52+Projection!J51)*(1+G53)</f>
+        <v>59320.0518417989</v>
+      </c>
+      <c r="J53" s="49" t="n">
+        <f aca="false">I53/PRODUCT(1+H$7:H53)</f>
+        <v>59320.0518417989</v>
+      </c>
+      <c r="K53" s="50" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L53" s="50" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="M53" s="49" t="n">
+        <f aca="false">(M52+Projection!J51)*(1+K53)</f>
+        <v>132289.616915265</v>
+      </c>
+      <c r="N53" s="49" t="n">
+        <f aca="false">M53/PRODUCT(1+L$7:L53)</f>
+        <v>124683.899071881</v>
+      </c>
+      <c r="O53" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P53" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q53" s="49" t="n">
+        <f aca="false">(Q52+Projection!J51)*(1+O53)</f>
+        <v>62995.0194519725</v>
+      </c>
+      <c r="R53" s="49" t="n">
+        <f aca="false">Q53/PRODUCT(1+P$7:P53)</f>
+        <v>62995.0194519725</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="47" t="n">
+        <v>47</v>
+      </c>
+      <c r="B54" s="47" t="n">
+        <v>47</v>
+      </c>
+      <c r="C54" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D54" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="49" t="n">
+        <f aca="false">(E53+Projection!J52)*(1+C54)</f>
+        <v>134471.658157495</v>
+      </c>
+      <c r="F54" s="49" t="n">
+        <f aca="false">E54/(1+Inputs!B13)^(47+1)</f>
+        <v>134471.658157495</v>
+      </c>
+      <c r="G54" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H54" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="49" t="n">
+        <f aca="false">(I53+Projection!J52)*(1+G54)</f>
+        <v>63655.3733681876</v>
+      </c>
+      <c r="J54" s="49" t="n">
+        <f aca="false">I54/PRODUCT(1+H$7:H54)</f>
+        <v>63655.3733681876</v>
+      </c>
+      <c r="K54" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L54" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="49" t="n">
+        <f aca="false">(M53+Projection!J52)*(1+K54)</f>
+        <v>141367.96017143</v>
+      </c>
+      <c r="N54" s="49" t="n">
+        <f aca="false">M54/PRODUCT(1+L$7:L54)</f>
+        <v>141367.96017143</v>
+      </c>
+      <c r="O54" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P54" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q54" s="49" t="n">
+        <f aca="false">(Q53+Projection!J52)*(1+O54)</f>
+        <v>67569.2138730226</v>
+      </c>
+      <c r="R54" s="49" t="n">
+        <f aca="false">Q54/PRODUCT(1+P$7:P54)</f>
+        <v>67569.2138730226</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="47" t="n">
+        <v>48</v>
+      </c>
+      <c r="B55" s="47" t="n">
+        <v>48</v>
+      </c>
+      <c r="C55" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D55" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E55" s="49" t="n">
+        <f aca="false">(E54+Projection!J53)*(1+C55)</f>
+        <v>143698.991081817</v>
+      </c>
+      <c r="F55" s="49" t="n">
+        <f aca="false">E55/(1+Inputs!B13)^(48+1)</f>
+        <v>143698.991081817</v>
+      </c>
+      <c r="G55" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H55" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="49" t="n">
+        <f aca="false">(I54+Projection!J53)*(1+G55)</f>
+        <v>68279.6477812047</v>
+      </c>
+      <c r="J55" s="49" t="n">
+        <f aca="false">I55/PRODUCT(1+H$7:H55)</f>
+        <v>68279.6477812047</v>
+      </c>
+      <c r="K55" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L55" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="49" t="n">
+        <f aca="false">(M54+Projection!J53)*(1+K55)</f>
+        <v>151043.552726657</v>
+      </c>
+      <c r="N55" s="49" t="n">
+        <f aca="false">M55/PRODUCT(1+L$7:L55)</f>
+        <v>151043.552726657</v>
+      </c>
+      <c r="O55" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P55" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q55" s="49" t="n">
+        <f aca="false">(Q54+Projection!J53)*(1+O55)</f>
+        <v>72447.8879188539</v>
+      </c>
+      <c r="R55" s="49" t="n">
+        <f aca="false">Q55/PRODUCT(1+P$7:P55)</f>
+        <v>72447.8879188539</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="47" t="n">
+        <v>49</v>
+      </c>
+      <c r="B56" s="47" t="n">
+        <v>49</v>
+      </c>
+      <c r="C56" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D56" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E56" s="49" t="n">
+        <f aca="false">(E55+Projection!J54)*(1+C56)</f>
+        <v>153533.36445434</v>
+      </c>
+      <c r="F56" s="49" t="n">
+        <f aca="false">E56/(1+Inputs!B13)^(49+1)</f>
+        <v>153533.36445434</v>
+      </c>
+      <c r="G56" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H56" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I56" s="49" t="n">
+        <f aca="false">(I55+Projection!J54)*(1+G56)</f>
+        <v>73211.7638391885</v>
+      </c>
+      <c r="J56" s="49" t="n">
+        <f aca="false">I56/PRODUCT(1+H$7:H56)</f>
+        <v>73211.7638391885</v>
+      </c>
+      <c r="K56" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L56" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="49" t="n">
+        <f aca="false">(M55+Projection!J54)*(1+K56)</f>
+        <v>161355.322606096</v>
+      </c>
+      <c r="N56" s="49" t="n">
+        <f aca="false">M56/PRODUCT(1+L$7:L56)</f>
+        <v>161355.322606096</v>
+      </c>
+      <c r="O56" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P56" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q56" s="49" t="n">
+        <f aca="false">(Q55+Projection!J54)*(1+O56)</f>
+        <v>77650.9395857849</v>
+      </c>
+      <c r="R56" s="49" t="n">
+        <f aca="false">Q56/PRODUCT(1+P$7:P56)</f>
+        <v>77650.9395857849</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="B57" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="C57" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D57" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="49" t="n">
+        <f aca="false">(E56+Projection!J55)*(1+C57)</f>
+        <v>164014.344319245</v>
+      </c>
+      <c r="F57" s="49" t="n">
+        <f aca="false">E57/(1+Inputs!B13)^(50+1)</f>
+        <v>164014.344319245</v>
+      </c>
+      <c r="G57" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H57" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I57" s="49" t="n">
+        <f aca="false">(I56+Projection!J55)*(1+G57)</f>
+        <v>78471.8396641085</v>
+      </c>
+      <c r="J57" s="49" t="n">
+        <f aca="false">I57/PRODUCT(1+H$7:H57)</f>
+        <v>78471.8396641085</v>
+      </c>
+      <c r="K57" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L57" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="49" t="n">
+        <f aca="false">(M56+Projection!J55)*(1+K57)</f>
+        <v>172344.729750865</v>
+      </c>
+      <c r="N57" s="49" t="n">
+        <f aca="false">M57/PRODUCT(1+L$7:L57)</f>
+        <v>172344.729750865</v>
+      </c>
+      <c r="O57" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P57" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="49" t="n">
+        <f aca="false">(Q56+Projection!J55)*(1+O57)</f>
+        <v>83199.5618342337</v>
+      </c>
+      <c r="R57" s="49" t="n">
+        <f aca="false">Q57/PRODUCT(1+P$7:P57)</f>
+        <v>83199.5618342337</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="47" t="n">
+        <v>51</v>
+      </c>
+      <c r="B58" s="47" t="n">
+        <v>51</v>
+      </c>
+      <c r="C58" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D58" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E58" s="49" t="n">
+        <f aca="false">(E57+Projection!J56)*(1+C58)</f>
+        <v>175184.070131717</v>
+      </c>
+      <c r="F58" s="49" t="n">
+        <f aca="false">E58/(1+Inputs!B13)^(51+1)</f>
+        <v>175184.070131717</v>
+      </c>
+      <c r="G58" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H58" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I58" s="49" t="n">
+        <f aca="false">(I57+Projection!J56)*(1+G58)</f>
+        <v>84081.3026739972</v>
+      </c>
+      <c r="J58" s="49" t="n">
+        <f aca="false">I58/PRODUCT(1+H$7:H58)</f>
+        <v>84081.3026739972</v>
+      </c>
+      <c r="K58" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L58" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="49" t="n">
+        <f aca="false">(M57+Projection!J56)*(1+K58)</f>
+        <v>184055.930616392</v>
+      </c>
+      <c r="N58" s="49" t="n">
+        <f aca="false">M58/PRODUCT(1+L$7:L58)</f>
+        <v>184055.930616392</v>
+      </c>
+      <c r="O58" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P58" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="49" t="n">
+        <f aca="false">(Q57+Projection!J56)*(1+O58)</f>
+        <v>89116.3267851804</v>
+      </c>
+      <c r="R58" s="49" t="n">
+        <f aca="false">Q58/PRODUCT(1+P$7:P58)</f>
+        <v>89116.3267851804</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="47" t="n">
+        <v>52</v>
+      </c>
+      <c r="B59" s="47" t="n">
+        <v>52</v>
+      </c>
+      <c r="C59" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D59" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E59" s="49" t="n">
+        <f aca="false">(E58+Projection!J57)*(1+C59)</f>
+        <v>187087.422053817</v>
+      </c>
+      <c r="F59" s="49" t="n">
+        <f aca="false">E59/(1+Inputs!B13)^(52+1)</f>
+        <v>187087.422053817</v>
+      </c>
+      <c r="G59" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H59" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="49" t="n">
+        <f aca="false">(I58+Projection!J57)*(1+G59)</f>
+        <v>90062.9747113453</v>
+      </c>
+      <c r="J59" s="49" t="n">
+        <f aca="false">I59/PRODUCT(1+H$7:H59)</f>
+        <v>90062.9747113453</v>
+      </c>
+      <c r="K59" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L59" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="49" t="n">
+        <f aca="false">(M58+Projection!J57)*(1+K59)</f>
+        <v>196535.953469996</v>
+      </c>
+      <c r="N59" s="49" t="n">
+        <f aca="false">M59/PRODUCT(1+L$7:L59)</f>
+        <v>196535.953469996</v>
+      </c>
+      <c r="O59" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P59" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q59" s="49" t="n">
+        <f aca="false">(Q58+Projection!J57)*(1+O59)</f>
+        <v>95425.2753897555</v>
+      </c>
+      <c r="R59" s="49" t="n">
+        <f aca="false">Q59/PRODUCT(1+P$7:P59)</f>
+        <v>95425.2753897555</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="47" t="n">
+        <v>53</v>
+      </c>
+      <c r="B60" s="47" t="n">
+        <v>53</v>
+      </c>
+      <c r="C60" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D60" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="49" t="n">
+        <f aca="false">(E59+Projection!J58)*(1+C60)</f>
+        <v>199772.199124937</v>
+      </c>
+      <c r="F60" s="49" t="n">
+        <f aca="false">E60/(1+Inputs!B13)^(53+1)</f>
+        <v>199772.199124937</v>
+      </c>
+      <c r="G60" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H60" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="49" t="n">
+        <f aca="false">(I59+Projection!J58)*(1+G60)</f>
+        <v>96441.1627052038</v>
+      </c>
+      <c r="J60" s="49" t="n">
+        <f aca="false">I60/PRODUCT(1+H$7:H60)</f>
+        <v>96441.1627052038</v>
+      </c>
+      <c r="K60" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L60" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="49" t="n">
+        <f aca="false">(M59+Projection!J58)*(1+K60)</f>
+        <v>209834.885083167</v>
+      </c>
+      <c r="N60" s="49" t="n">
+        <f aca="false">M60/PRODUCT(1+L$7:L60)</f>
+        <v>209834.885083167</v>
+      </c>
+      <c r="O60" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P60" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q60" s="49" t="n">
+        <f aca="false">(Q59+Projection!J58)*(1+O60)</f>
+        <v>102152.012927711</v>
+      </c>
+      <c r="R60" s="49" t="n">
+        <f aca="false">Q60/PRODUCT(1+P$7:P60)</f>
+        <v>102152.012927711</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="47" t="n">
+        <v>54</v>
+      </c>
+      <c r="B61" s="47" t="n">
+        <v>54</v>
+      </c>
+      <c r="C61" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D61" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="49" t="n">
+        <f aca="false">(E60+Projection!J59)*(1+C61)</f>
+        <v>213289.309013703</v>
+      </c>
+      <c r="F61" s="49" t="n">
+        <f aca="false">E61/(1+Inputs!B13)^(54+1)</f>
+        <v>213289.309013703</v>
+      </c>
+      <c r="G61" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H61" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="49" t="n">
+        <f aca="false">(I60+Projection!J59)*(1+G61)</f>
+        <v>103241.755226687</v>
+      </c>
+      <c r="J61" s="49" t="n">
+        <f aca="false">I61/PRODUCT(1+H$7:H61)</f>
+        <v>103241.755226687</v>
+      </c>
+      <c r="K61" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L61" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="49" t="n">
+        <f aca="false">(M60+Projection!J59)*(1+K61)</f>
+        <v>224006.069559218</v>
+      </c>
+      <c r="N61" s="49" t="n">
+        <f aca="false">M61/PRODUCT(1+L$7:L61)</f>
+        <v>224006.069559218</v>
+      </c>
+      <c r="O61" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P61" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q61" s="49" t="n">
+        <f aca="false">(Q60+Projection!J59)*(1+O61)</f>
+        <v>109323.810713657</v>
+      </c>
+      <c r="R61" s="49" t="n">
+        <f aca="false">Q61/PRODUCT(1+P$7:P61)</f>
+        <v>109323.810713657</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="47" t="n">
+        <v>55</v>
+      </c>
+      <c r="B62" s="47" t="n">
+        <v>55</v>
+      </c>
+      <c r="C62" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D62" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="49" t="n">
+        <f aca="false">(E61+Projection!J60)*(1+C62)</f>
+        <v>227692.970104129</v>
+      </c>
+      <c r="F62" s="49" t="n">
+        <f aca="false">E62/(1+Inputs!B13)^(55+1)</f>
+        <v>227692.970104129</v>
+      </c>
+      <c r="G62" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H62" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="49" t="n">
+        <f aca="false">(I61+Projection!J60)*(1+G62)</f>
+        <v>110492.325320957</v>
+      </c>
+      <c r="J62" s="49" t="n">
+        <f aca="false">I62/PRODUCT(1+H$7:H62)</f>
+        <v>110492.325320957</v>
+      </c>
+      <c r="K62" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L62" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M62" s="49" t="n">
+        <f aca="false">(M61+Projection!J60)*(1+K62)</f>
+        <v>239106.320085103</v>
+      </c>
+      <c r="N62" s="49" t="n">
+        <f aca="false">M62/PRODUCT(1+L$7:L62)</f>
+        <v>239106.320085103</v>
+      </c>
+      <c r="O62" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P62" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q62" s="49" t="n">
+        <f aca="false">(Q61+Projection!J60)*(1+O62)</f>
+        <v>116969.71441458</v>
+      </c>
+      <c r="R62" s="49" t="n">
+        <f aca="false">Q62/PRODUCT(1+P$7:P62)</f>
+        <v>116969.71441458</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="47" t="n">
+        <v>56</v>
+      </c>
+      <c r="B63" s="47" t="n">
+        <v>56</v>
+      </c>
+      <c r="C63" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D63" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="49" t="n">
+        <f aca="false">(E62+Projection!J61)*(1+C63)</f>
+        <v>243040.926717739</v>
+      </c>
+      <c r="F63" s="49" t="n">
+        <f aca="false">E63/(1+Inputs!B13)^(56+1)</f>
+        <v>243040.926717739</v>
+      </c>
+      <c r="G63" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H63" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="49" t="n">
+        <f aca="false">(I62+Projection!J61)*(1+G63)</f>
+        <v>118222.240023661</v>
+      </c>
+      <c r="J63" s="49" t="n">
+        <f aca="false">I63/PRODUCT(1+H$7:H63)</f>
+        <v>118222.240023661</v>
+      </c>
+      <c r="K63" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L63" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M63" s="49" t="n">
+        <f aca="false">(M62+Projection!J61)*(1+K63)</f>
+        <v>255196.144447476</v>
+      </c>
+      <c r="N63" s="49" t="n">
+        <f aca="false">M63/PRODUCT(1+L$7:L63)</f>
+        <v>255196.144447476</v>
+      </c>
+      <c r="O63" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P63" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q63" s="49" t="n">
+        <f aca="false">(Q62+Projection!J61)*(1+O63)</f>
+        <v>125120.65940837</v>
+      </c>
+      <c r="R63" s="49" t="n">
+        <f aca="false">Q63/PRODUCT(1+P$7:P63)</f>
+        <v>125120.65940837</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="47" t="n">
+        <v>57</v>
+      </c>
+      <c r="B64" s="47" t="n">
+        <v>57</v>
+      </c>
+      <c r="C64" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D64" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E64" s="49" t="n">
+        <f aca="false">(E63+Projection!J62)*(1+C64)</f>
+        <v>259394.678325515</v>
+      </c>
+      <c r="F64" s="49" t="n">
+        <f aca="false">E64/(1+Inputs!B13)^(57+1)</f>
+        <v>259394.678325515</v>
+      </c>
+      <c r="G64" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H64" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I64" s="49" t="n">
+        <f aca="false">(I63+Projection!J62)*(1+G64)</f>
+        <v>126462.776996323</v>
+      </c>
+      <c r="J64" s="49" t="n">
+        <f aca="false">I64/PRODUCT(1+H$7:H64)</f>
+        <v>126462.776996323</v>
+      </c>
+      <c r="K64" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L64" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M64" s="49" t="n">
+        <f aca="false">(M63+Projection!J62)*(1+K64)</f>
+        <v>272339.985207685</v>
+      </c>
+      <c r="N64" s="49" t="n">
+        <f aca="false">M64/PRODUCT(1+L$7:L64)</f>
+        <v>272339.985207685</v>
+      </c>
+      <c r="O64" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P64" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q64" s="49" t="n">
+        <f aca="false">(Q63+Projection!J62)*(1+O64)</f>
+        <v>133809.593641037</v>
+      </c>
+      <c r="R64" s="49" t="n">
+        <f aca="false">Q64/PRODUCT(1+P$7:P64)</f>
+        <v>133809.593641037</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="47" t="n">
+        <v>58</v>
+      </c>
+      <c r="B65" s="47" t="n">
+        <v>58</v>
+      </c>
+      <c r="C65" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D65" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E65" s="49" t="n">
+        <f aca="false">(E64+Projection!J63)*(1+C65)</f>
+        <v>276819.723659008</v>
+      </c>
+      <c r="F65" s="49" t="n">
+        <f aca="false">E65/(1+Inputs!B13)^(58+1)</f>
+        <v>276819.723659008</v>
+      </c>
+      <c r="G65" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H65" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I65" s="49" t="n">
+        <f aca="false">(I64+Projection!J63)*(1+G65)</f>
+        <v>135247.248743418</v>
+      </c>
+      <c r="J65" s="49" t="n">
+        <f aca="false">I65/PRODUCT(1+H$7:H65)</f>
+        <v>135247.248743418</v>
+      </c>
+      <c r="K65" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L65" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="49" t="n">
+        <f aca="false">(M64+Projection!J63)*(1+K65)</f>
+        <v>290606.475488519</v>
+      </c>
+      <c r="N65" s="49" t="n">
+        <f aca="false">M65/PRODUCT(1+L$7:L65)</f>
+        <v>290606.475488519</v>
+      </c>
+      <c r="O65" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P65" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q65" s="49" t="n">
+        <f aca="false">(Q64+Projection!J63)*(1+O65)</f>
+        <v>143071.608470038</v>
+      </c>
+      <c r="R65" s="49" t="n">
+        <f aca="false">Q65/PRODUCT(1+P$7:P65)</f>
+        <v>143071.608470038</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="47" t="n">
+        <v>59</v>
+      </c>
+      <c r="B66" s="47" t="n">
+        <v>59</v>
+      </c>
+      <c r="C66" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D66" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E66" s="49" t="n">
+        <f aca="false">(E65+Projection!J64)*(1+C66)</f>
+        <v>295385.820689063</v>
+      </c>
+      <c r="F66" s="49" t="n">
+        <f aca="false">E66/(1+Inputs!B13)^(59+1)</f>
+        <v>295385.820689063</v>
+      </c>
+      <c r="G66" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H66" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I66" s="49" t="n">
+        <f aca="false">(I65+Projection!J64)*(1+G66)</f>
+        <v>144611.134903959</v>
+      </c>
+      <c r="J66" s="49" t="n">
+        <f aca="false">I66/PRODUCT(1+H$7:H66)</f>
+        <v>144611.134903959</v>
+      </c>
+      <c r="K66" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L66" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M66" s="49" t="n">
+        <f aca="false">(M65+Projection!J64)*(1+K66)</f>
+        <v>310068.711387492</v>
+      </c>
+      <c r="N66" s="49" t="n">
+        <f aca="false">M66/PRODUCT(1+L$7:L66)</f>
+        <v>310068.711387492</v>
+      </c>
+      <c r="O66" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P66" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q66" s="49" t="n">
+        <f aca="false">(Q65+Projection!J64)*(1+O66)</f>
+        <v>152944.07801281</v>
+      </c>
+      <c r="R66" s="49" t="n">
+        <f aca="false">Q66/PRODUCT(1+P$7:P66)</f>
+        <v>152944.07801281</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="47" t="n">
+        <v>60</v>
+      </c>
+      <c r="B67" s="47" t="n">
+        <v>60</v>
+      </c>
+      <c r="C67" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D67" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E67" s="49" t="n">
+        <f aca="false">(E66+Projection!J65)*(1+C67)</f>
+        <v>315167.263503567</v>
+      </c>
+      <c r="F67" s="49" t="n">
+        <f aca="false">E67/(1+Inputs!B13)^(60+1)</f>
+        <v>315167.263503567</v>
+      </c>
+      <c r="G67" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H67" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I67" s="49" t="n">
+        <f aca="false">(I66+Projection!J65)*(1+G67)</f>
+        <v>154592.223142432</v>
+      </c>
+      <c r="J67" s="49" t="n">
+        <f aca="false">I67/PRODUCT(1+H$7:H67)</f>
+        <v>154592.223142432</v>
+      </c>
+      <c r="K67" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L67" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M67" s="49" t="n">
+        <f aca="false">(M66+Projection!J65)*(1+K67)</f>
+        <v>330804.542097394</v>
+      </c>
+      <c r="N67" s="49" t="n">
+        <f aca="false">M67/PRODUCT(1+L$7:L67)</f>
+        <v>330804.542097394</v>
+      </c>
+      <c r="O67" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P67" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q67" s="49" t="n">
+        <f aca="false">(Q66+Projection!J65)*(1+O67)</f>
+        <v>163466.807553358</v>
+      </c>
+      <c r="R67" s="49" t="n">
+        <f aca="false">Q67/PRODUCT(1+P$7:P67)</f>
+        <v>163466.807553358</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="47" t="n">
+        <v>61</v>
+      </c>
+      <c r="B68" s="47" t="n">
+        <v>61</v>
+      </c>
+      <c r="C68" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D68" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E68" s="49" t="n">
+        <f aca="false">(E67+Projection!J66)*(1+C68)</f>
+        <v>336243.177182652</v>
+      </c>
+      <c r="F68" s="49" t="n">
+        <f aca="false">E68/(1+Inputs!B13)^(61+1)</f>
+        <v>336243.177182652</v>
+      </c>
+      <c r="G68" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H68" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="49" t="n">
+        <f aca="false">(I67+Projection!J66)*(1+G68)</f>
+        <v>165230.759198043</v>
+      </c>
+      <c r="J68" s="49" t="n">
+        <f aca="false">I68/PRODUCT(1+H$7:H68)</f>
+        <v>165230.759198043</v>
+      </c>
+      <c r="K68" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L68" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M68" s="49" t="n">
+        <f aca="false">(M67+Projection!J66)*(1+K68)</f>
+        <v>352896.878885078</v>
+      </c>
+      <c r="N68" s="49" t="n">
+        <f aca="false">M68/PRODUCT(1+L$7:L68)</f>
+        <v>352896.878885078</v>
+      </c>
+      <c r="O68" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P68" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q68" s="49" t="n">
+        <f aca="false">(Q67+Projection!J66)*(1+O68)</f>
+        <v>174682.19159568</v>
+      </c>
+      <c r="R68" s="49" t="n">
+        <f aca="false">Q68/PRODUCT(1+P$7:P68)</f>
+        <v>174682.19159568</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="47" t="n">
+        <v>62</v>
+      </c>
+      <c r="B69" s="47" t="n">
+        <v>62</v>
+      </c>
+      <c r="C69" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D69" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E69" s="49" t="n">
+        <f aca="false">(E68+Projection!J67)*(1+C69)</f>
+        <v>358697.831841196</v>
+      </c>
+      <c r="F69" s="49" t="n">
+        <f aca="false">E69/(1+Inputs!B13)^(62+1)</f>
+        <v>358697.831841196</v>
+      </c>
+      <c r="G69" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H69" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I69" s="49" t="n">
+        <f aca="false">(I68+Projection!J67)*(1+G69)</f>
+        <v>176569.606687587</v>
+      </c>
+      <c r="J69" s="49" t="n">
+        <f aca="false">I69/PRODUCT(1+H$7:H69)</f>
+        <v>176569.606687587</v>
+      </c>
+      <c r="K69" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L69" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M69" s="49" t="n">
+        <f aca="false">(M68+Projection!J67)*(1+K69)</f>
+        <v>376434.024154279</v>
+      </c>
+      <c r="N69" s="49" t="n">
+        <f aca="false">M69/PRODUCT(1+L$7:L69)</f>
+        <v>376434.024154279</v>
+      </c>
+      <c r="O69" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P69" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q69" s="49" t="n">
+        <f aca="false">(Q68+Projection!J67)*(1+O69)</f>
+        <v>186635.38219107</v>
+      </c>
+      <c r="R69" s="49" t="n">
+        <f aca="false">Q69/PRODUCT(1+P$7:P69)</f>
+        <v>186635.38219107</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="47" t="n">
+        <v>63</v>
+      </c>
+      <c r="B70" s="47" t="n">
+        <v>63</v>
+      </c>
+      <c r="C70" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D70" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E70" s="49" t="n">
+        <f aca="false">(E69+Projection!J68)*(1+C70)</f>
+        <v>382620.97708451</v>
+      </c>
+      <c r="F70" s="49" t="n">
+        <f aca="false">E70/(1+Inputs!B13)^(63+1)</f>
+        <v>382620.97708451</v>
+      </c>
+      <c r="G70" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H70" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I70" s="49" t="n">
+        <f aca="false">(I69+Projection!J68)*(1+G70)</f>
+        <v>188654.417295917</v>
+      </c>
+      <c r="J70" s="49" t="n">
+        <f aca="false">I70/PRODUCT(1+H$7:H70)</f>
+        <v>188654.417295917</v>
+      </c>
+      <c r="K70" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L70" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M70" s="49" t="n">
+        <f aca="false">(M69+Projection!J68)*(1+K70)</f>
+        <v>401510.021897944</v>
+      </c>
+      <c r="N70" s="49" t="n">
+        <f aca="false">M70/PRODUCT(1+L$7:L70)</f>
+        <v>401510.021897944</v>
+      </c>
+      <c r="O70" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P70" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q70" s="49" t="n">
+        <f aca="false">(Q69+Projection!J68)*(1+O70)</f>
+        <v>199374.468207127</v>
+      </c>
+      <c r="R70" s="49" t="n">
+        <f aca="false">Q70/PRODUCT(1+P$7:P70)</f>
+        <v>199374.468207127</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="47" t="n">
+        <v>64</v>
+      </c>
+      <c r="B71" s="47" t="n">
+        <v>64</v>
+      </c>
+      <c r="C71" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D71" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E71" s="49" t="n">
+        <f aca="false">(E70+Projection!J69)*(1+C71)</f>
+        <v>408108.198204068</v>
+      </c>
+      <c r="F71" s="49" t="n">
+        <f aca="false">E71/(1+Inputs!B13)^(64+1)</f>
+        <v>408108.198204068</v>
+      </c>
+      <c r="G71" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H71" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I71" s="49" t="n">
+        <f aca="false">(I70+Projection!J69)*(1+G71)</f>
+        <v>201533.812029216</v>
+      </c>
+      <c r="J71" s="49" t="n">
+        <f aca="false">I71/PRODUCT(1+H$7:H71)</f>
+        <v>201533.812029216</v>
+      </c>
+      <c r="K71" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L71" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M71" s="49" t="n">
+        <f aca="false">(M70+Projection!J69)*(1+K71)</f>
+        <v>428225.030930375</v>
+      </c>
+      <c r="N71" s="49" t="n">
+        <f aca="false">M71/PRODUCT(1+L$7:L71)</f>
+        <v>428225.030930375</v>
+      </c>
+      <c r="O71" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P71" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q71" s="49" t="n">
+        <f aca="false">(Q70+Projection!J69)*(1+O71)</f>
+        <v>212950.666249654</v>
+      </c>
+      <c r="R71" s="49" t="n">
+        <f aca="false">Q71/PRODUCT(1+P$7:P71)</f>
+        <v>212950.666249654</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="47" t="n">
+        <v>65</v>
+      </c>
+      <c r="B72" s="47" t="n">
+        <v>65</v>
+      </c>
+      <c r="C72" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D72" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E72" s="49" t="n">
+        <f aca="false">(E71+Projection!J70)*(1+C72)</f>
+        <v>435261.295526382</v>
+      </c>
+      <c r="F72" s="49" t="n">
+        <f aca="false">E72/(1+Inputs!B13)^(65+1)</f>
+        <v>435261.295526382</v>
+      </c>
+      <c r="G72" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H72" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I72" s="49" t="n">
+        <f aca="false">(I71+Projection!J70)*(1+G72)</f>
+        <v>215259.574250165</v>
+      </c>
+      <c r="J72" s="49" t="n">
+        <f aca="false">I72/PRODUCT(1+H$7:H72)</f>
+        <v>215259.574250165</v>
+      </c>
+      <c r="K72" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L72" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M72" s="49" t="n">
+        <f aca="false">(M71+Projection!J70)*(1+K72)</f>
+        <v>456685.7223799</v>
+      </c>
+      <c r="N72" s="49" t="n">
+        <f aca="false">M72/PRODUCT(1+L$7:L72)</f>
+        <v>456685.7223799</v>
+      </c>
+      <c r="O72" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P72" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q72" s="49" t="n">
+        <f aca="false">(Q71+Projection!J70)*(1+O72)</f>
+        <v>227418.523994932</v>
+      </c>
+      <c r="R72" s="49" t="n">
+        <f aca="false">Q72/PRODUCT(1+P$7:P72)</f>
+        <v>227418.523994932</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="47" t="n">
+        <v>66</v>
+      </c>
+      <c r="B73" s="47" t="n">
+        <v>66</v>
+      </c>
+      <c r="C73" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D73" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E73" s="49" t="n">
+        <f aca="false">(E72+Projection!J71)*(1+C73)</f>
+        <v>464188.688420006</v>
+      </c>
+      <c r="F73" s="49" t="n">
+        <f aca="false">E73/(1+Inputs!B13)^(66+1)</f>
+        <v>464188.688420006</v>
+      </c>
+      <c r="G73" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H73" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I73" s="49" t="n">
+        <f aca="false">(I72+Projection!J71)*(1+G73)</f>
+        <v>229886.855260835</v>
+      </c>
+      <c r="J73" s="49" t="n">
+        <f aca="false">I73/PRODUCT(1+H$7:H73)</f>
+        <v>229886.855260835</v>
+      </c>
+      <c r="K73" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L73" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M73" s="49" t="n">
+        <f aca="false">(M72+Projection!J71)*(1+K73)</f>
+        <v>487005.703019002</v>
+      </c>
+      <c r="N73" s="49" t="n">
+        <f aca="false">M73/PRODUCT(1+L$7:L73)</f>
+        <v>487005.703019002</v>
+      </c>
+      <c r="O73" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P73" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q73" s="49" t="n">
+        <f aca="false">(Q72+Projection!J71)*(1+O73)</f>
+        <v>242836.136739012</v>
+      </c>
+      <c r="R73" s="49" t="n">
+        <f aca="false">Q73/PRODUCT(1+P$7:P73)</f>
+        <v>242836.136739012</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="47" t="n">
+        <v>67</v>
+      </c>
+      <c r="B74" s="47" t="n">
+        <v>67</v>
+      </c>
+      <c r="C74" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D74" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E74" s="49" t="n">
+        <f aca="false">(E73+Projection!J72)*(1+C74)</f>
+        <v>495005.845563424</v>
+      </c>
+      <c r="F74" s="49" t="n">
+        <f aca="false">E74/(1+Inputs!B13)^(67+1)</f>
+        <v>495005.845563424</v>
+      </c>
+      <c r="G74" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H74" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I74" s="49" t="n">
+        <f aca="false">(I73+Projection!J72)*(1+G74)</f>
+        <v>245474.393248907</v>
+      </c>
+      <c r="J74" s="49" t="n">
+        <f aca="false">I74/PRODUCT(1+H$7:H74)</f>
+        <v>245474.393248907</v>
+      </c>
+      <c r="K74" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L74" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M74" s="49" t="n">
+        <f aca="false">(M73+Projection!J72)*(1+K74)</f>
+        <v>519305.966111354</v>
+      </c>
+      <c r="N74" s="49" t="n">
+        <f aca="false">M74/PRODUCT(1+L$7:L74)</f>
+        <v>519305.966111354</v>
+      </c>
+      <c r="O74" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P74" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q74" s="49" t="n">
+        <f aca="false">(Q73+Projection!J72)*(1+O74)</f>
+        <v>259265.378023164</v>
+      </c>
+      <c r="R74" s="49" t="n">
+        <f aca="false">Q74/PRODUCT(1+P$7:P74)</f>
+        <v>259265.378023164</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="47" t="n">
+        <v>68</v>
+      </c>
+      <c r="B75" s="47" t="n">
+        <v>68</v>
+      </c>
+      <c r="C75" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D75" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E75" s="49" t="n">
+        <f aca="false">(E74+Projection!J73)*(1+C75)</f>
+        <v>527835.743180807</v>
+      </c>
+      <c r="F75" s="49" t="n">
+        <f aca="false">E75/(1+Inputs!B13)^(68+1)</f>
+        <v>527835.743180807</v>
+      </c>
+      <c r="G75" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H75" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I75" s="49" t="n">
+        <f aca="false">(I74+Projection!J73)*(1+G75)</f>
+        <v>262084.746465846</v>
+      </c>
+      <c r="J75" s="49" t="n">
+        <f aca="false">I75/PRODUCT(1+H$7:H75)</f>
+        <v>262084.746465846</v>
+      </c>
+      <c r="K75" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L75" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M75" s="49" t="n">
+        <f aca="false">(M74+Projection!J73)*(1+K75)</f>
+        <v>553715.371564353</v>
+      </c>
+      <c r="N75" s="49" t="n">
+        <f aca="false">M75/PRODUCT(1+L$7:L75)</f>
+        <v>553715.371564353</v>
+      </c>
+      <c r="O75" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P75" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q75" s="49" t="n">
+        <f aca="false">(Q74+Projection!J73)*(1+O75)</f>
+        <v>276772.14525043</v>
+      </c>
+      <c r="R75" s="49" t="n">
+        <f aca="false">Q75/PRODUCT(1+P$7:P75)</f>
+        <v>276772.14525043</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="B76" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="C76" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D76" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E76" s="49" t="n">
+        <f aca="false">(E75+Projection!J74)*(1+C76)</f>
+        <v>562809.353063555</v>
+      </c>
+      <c r="F76" s="49" t="n">
+        <f aca="false">E76/(1+Inputs!B13)^(69+1)</f>
+        <v>562809.353063555</v>
+      </c>
+      <c r="G76" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H76" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="49" t="n">
+        <f aca="false">(I75+Projection!J74)*(1+G76)</f>
+        <v>279784.541562121</v>
+      </c>
+      <c r="J76" s="49" t="n">
+        <f aca="false">I76/PRODUCT(1+H$7:H76)</f>
+        <v>279784.541562121</v>
+      </c>
+      <c r="K76" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L76" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M76" s="49" t="n">
+        <f aca="false">(M75+Projection!J74)*(1+K76)</f>
+        <v>590371.157292031</v>
+      </c>
+      <c r="N76" s="49" t="n">
+        <f aca="false">M76/PRODUCT(1+L$7:L76)</f>
+        <v>590371.157292031</v>
+      </c>
+      <c r="O76" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P76" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q76" s="49" t="n">
+        <f aca="false">(Q75+Projection!J74)*(1+O76)</f>
+        <v>295426.621267704</v>
+      </c>
+      <c r="R76" s="49" t="n">
+        <f aca="false">Q76/PRODUCT(1+P$7:P76)</f>
+        <v>295426.621267704</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="47" t="n">
+        <v>70</v>
+      </c>
+      <c r="B77" s="47" t="n">
+        <v>70</v>
+      </c>
+      <c r="C77" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D77" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E77" s="49" t="n">
+        <f aca="false">(E76+Projection!J75)*(1+C77)</f>
+        <v>600066.162313696</v>
+      </c>
+      <c r="F77" s="49" t="n">
+        <f aca="false">E77/(1+Inputs!B13)^(70+1)</f>
+        <v>600066.162313696</v>
+      </c>
+      <c r="G77" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H77" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I77" s="49" t="n">
+        <f aca="false">(I76+Projection!J75)*(1+G77)</f>
+        <v>298644.73806467</v>
+      </c>
+      <c r="J77" s="49" t="n">
+        <f aca="false">I77/PRODUCT(1+H$7:H77)</f>
+        <v>298644.73806467</v>
+      </c>
+      <c r="K77" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L77" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M77" s="49" t="n">
+        <f aca="false">(M76+Projection!J75)*(1+K77)</f>
+        <v>629419.483817024</v>
+      </c>
+      <c r="N77" s="49" t="n">
+        <f aca="false">M77/PRODUCT(1+L$7:L77)</f>
+        <v>629419.483817024</v>
+      </c>
+      <c r="O77" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P77" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q77" s="49" t="n">
+        <f aca="false">(Q76+Projection!J75)*(1+O77)</f>
+        <v>315303.552951115</v>
+      </c>
+      <c r="R77" s="49" t="n">
+        <f aca="false">Q77/PRODUCT(1+P$7:P77)</f>
+        <v>315303.552951115</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="47" t="n">
+        <v>71</v>
+      </c>
+      <c r="B78" s="47" t="n">
+        <v>71</v>
+      </c>
+      <c r="C78" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D78" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E78" s="49" t="n">
+        <f aca="false">(E77+Projection!J76)*(1+C78)</f>
+        <v>639754.726871082</v>
+      </c>
+      <c r="F78" s="49" t="n">
+        <f aca="false">E78/(1+Inputs!B13)^(71+1)</f>
+        <v>639754.726871082</v>
+      </c>
+      <c r="G78" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H78" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I78" s="49" t="n">
+        <f aca="false">(I77+Projection!J76)*(1+G78)</f>
+        <v>318740.910045869</v>
+      </c>
+      <c r="J78" s="49" t="n">
+        <f aca="false">I78/PRODUCT(1+H$7:H78)</f>
+        <v>318740.910045869</v>
+      </c>
+      <c r="K78" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L78" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M78" s="49" t="n">
+        <f aca="false">(M77+Projection!J76)*(1+K78)</f>
+        <v>671016.014272126</v>
+      </c>
+      <c r="N78" s="49" t="n">
+        <f aca="false">M78/PRODUCT(1+L$7:L78)</f>
+        <v>671016.014272126</v>
+      </c>
+      <c r="O78" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P78" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q78" s="49" t="n">
+        <f aca="false">(Q77+Projection!J76)*(1+O78)</f>
+        <v>336482.547899933</v>
+      </c>
+      <c r="R78" s="49" t="n">
+        <f aca="false">Q78/PRODUCT(1+P$7:P78)</f>
+        <v>336482.547899933</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="47" t="n">
+        <v>72</v>
+      </c>
+      <c r="B79" s="47" t="n">
+        <v>72</v>
+      </c>
+      <c r="C79" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D79" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E79" s="49" t="n">
+        <f aca="false">(E78+Projection!J77)*(1+C79)</f>
+        <v>682033.261020325</v>
+      </c>
+      <c r="F79" s="49" t="n">
+        <f aca="false">E79/(1+Inputs!B13)^(72+1)</f>
+        <v>682033.261020325</v>
+      </c>
+      <c r="G79" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H79" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I79" s="49" t="n">
+        <f aca="false">(I78+Projection!J77)*(1+G79)</f>
+        <v>340153.546101473</v>
+      </c>
+      <c r="J79" s="49" t="n">
+        <f aca="false">I79/PRODUCT(1+H$7:H79)</f>
+        <v>340153.546101473</v>
+      </c>
+      <c r="K79" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L79" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M79" s="49" t="n">
+        <f aca="false">(M78+Projection!J77)*(1+K79)</f>
+        <v>715326.532102436</v>
+      </c>
+      <c r="N79" s="49" t="n">
+        <f aca="false">M79/PRODUCT(1+L$7:L79)</f>
+        <v>715326.532102436</v>
+      </c>
+      <c r="O79" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P79" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q79" s="49" t="n">
+        <f aca="false">(Q78+Projection!J77)*(1+O79)</f>
+        <v>359048.390416052</v>
+      </c>
+      <c r="R79" s="49" t="n">
+        <f aca="false">Q79/PRODUCT(1+P$7:P79)</f>
+        <v>359048.390416052</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="47" t="n">
+        <v>73</v>
+      </c>
+      <c r="B80" s="47" t="n">
+        <v>73</v>
+      </c>
+      <c r="C80" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D80" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E80" s="49" t="n">
+        <f aca="false">(E79+Projection!J78)*(1+C80)</f>
+        <v>727070.265216173</v>
+      </c>
+      <c r="F80" s="49" t="n">
+        <f aca="false">E80/(1+Inputs!B13)^(73+1)</f>
+        <v>727070.265216173</v>
+      </c>
+      <c r="G80" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H80" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I80" s="49" t="n">
+        <f aca="false">(I79+Projection!J78)*(1+G80)</f>
+        <v>362968.368827596</v>
+      </c>
+      <c r="J80" s="49" t="n">
+        <f aca="false">I80/PRODUCT(1+H$7:H80)</f>
+        <v>362968.368827596</v>
+      </c>
+      <c r="K80" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L80" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M80" s="49" t="n">
+        <f aca="false">(M79+Projection!J78)*(1+K80)</f>
+        <v>762527.598918622</v>
+      </c>
+      <c r="N80" s="49" t="n">
+        <f aca="false">M80/PRODUCT(1+L$7:L80)</f>
+        <v>762527.598918622</v>
+      </c>
+      <c r="O80" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P80" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q80" s="49" t="n">
+        <f aca="false">(Q79+Projection!J78)*(1+O80)</f>
+        <v>383091.378022622</v>
+      </c>
+      <c r="R80" s="49" t="n">
+        <f aca="false">Q80/PRODUCT(1+P$7:P80)</f>
+        <v>383091.378022622</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="47" t="n">
+        <v>74</v>
+      </c>
+      <c r="B81" s="47" t="n">
+        <v>74</v>
+      </c>
+      <c r="C81" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D81" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E81" s="49" t="n">
+        <f aca="false">(E80+Projection!J79)*(1+C81)</f>
+        <v>775045.194718028</v>
+      </c>
+      <c r="F81" s="49" t="n">
+        <f aca="false">E81/(1+Inputs!B13)^(74+1)</f>
+        <v>775045.194718028</v>
+      </c>
+      <c r="G81" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H81" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I81" s="49" t="n">
+        <f aca="false">(I80+Projection!J79)*(1+G81)</f>
+        <v>387276.675064194</v>
+      </c>
+      <c r="J81" s="49" t="n">
+        <f aca="false">I81/PRODUCT(1+H$7:H81)</f>
+        <v>387276.675064194</v>
+      </c>
+      <c r="K81" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L81" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M81" s="49" t="n">
+        <f aca="false">(M80+Projection!J79)*(1+K81)</f>
+        <v>812807.255111136</v>
+      </c>
+      <c r="N81" s="49" t="n">
+        <f aca="false">M81/PRODUCT(1+L$7:L81)</f>
+        <v>812807.255111136</v>
+      </c>
+      <c r="O81" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P81" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q81" s="49" t="n">
+        <f aca="false">(Q80+Projection!J79)*(1+O81)</f>
+        <v>408707.679856896</v>
+      </c>
+      <c r="R81" s="49" t="n">
+        <f aca="false">Q81/PRODUCT(1+P$7:P81)</f>
+        <v>408707.679856896</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="47" t="n">
+        <v>75</v>
+      </c>
+      <c r="B82" s="47" t="n">
+        <v>75</v>
+      </c>
+      <c r="C82" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D82" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E82" s="49" t="n">
+        <f aca="false">(E81+Projection!J80)*(1+C82)</f>
+        <v>826149.171686202</v>
+      </c>
+      <c r="F82" s="49" t="n">
+        <f aca="false">E82/(1+Inputs!B13)^(75+1)</f>
+        <v>826149.171686202</v>
+      </c>
+      <c r="G82" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H82" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I82" s="49" t="n">
+        <f aca="false">(I81+Projection!J80)*(1+G82)</f>
+        <v>413175.698254869</v>
+      </c>
+      <c r="J82" s="49" t="n">
+        <f aca="false">I82/PRODUCT(1+H$7:H82)</f>
+        <v>413175.698254869</v>
+      </c>
+      <c r="K82" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L82" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M82" s="49" t="n">
+        <f aca="false">(M81+Projection!J80)*(1+K82)</f>
+        <v>866365.766004862</v>
+      </c>
+      <c r="N82" s="49" t="n">
+        <f aca="false">M82/PRODUCT(1+L$7:L82)</f>
+        <v>866365.766004862</v>
+      </c>
+      <c r="O82" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P82" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q82" s="49" t="n">
+        <f aca="false">(Q81+Projection!J80)*(1+O82)</f>
+        <v>435999.718359097</v>
+      </c>
+      <c r="R82" s="49" t="n">
+        <f aca="false">Q82/PRODUCT(1+P$7:P82)</f>
+        <v>435999.718359097</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="47" t="n">
+        <v>76</v>
+      </c>
+      <c r="B83" s="47" t="n">
+        <v>76</v>
+      </c>
+      <c r="C83" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D83" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E83" s="49" t="n">
+        <f aca="false">(E82+Projection!J81)*(1+C83)</f>
+        <v>880585.743564942</v>
+      </c>
+      <c r="F83" s="49" t="n">
+        <f aca="false">E83/(1+Inputs!B13)^(76+1)</f>
+        <v>880585.743564942</v>
+      </c>
+      <c r="G83" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H83" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I83" s="49" t="n">
+        <f aca="false">(I82+Projection!J81)*(1+G83)</f>
+        <v>440768.994360572</v>
+      </c>
+      <c r="J83" s="49" t="n">
+        <f aca="false">I83/PRODUCT(1+H$7:H83)</f>
+        <v>440768.994360572</v>
+      </c>
+      <c r="K83" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L83" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M83" s="49" t="n">
+        <f aca="false">(M82+Projection!J81)*(1+K83)</f>
+        <v>923416.416514315</v>
+      </c>
+      <c r="N83" s="49" t="n">
+        <f aca="false">M83/PRODUCT(1+L$7:L83)</f>
+        <v>923416.416514315</v>
+      </c>
+      <c r="O83" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P83" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q83" s="49" t="n">
+        <f aca="false">(Q82+Projection!J81)*(1+O83)</f>
+        <v>465076.575771575</v>
+      </c>
+      <c r="R83" s="49" t="n">
+        <f aca="false">Q83/PRODUCT(1+P$7:P83)</f>
+        <v>465076.575771575</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="47" t="n">
+        <v>77</v>
+      </c>
+      <c r="B84" s="47" t="n">
+        <v>77</v>
+      </c>
+      <c r="C84" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D84" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E84" s="49" t="n">
+        <f aca="false">(E83+Projection!J82)*(1+C84)</f>
+        <v>938571.690760862</v>
+      </c>
+      <c r="F84" s="49" t="n">
+        <f aca="false">E84/(1+Inputs!B13)^(77+1)</f>
+        <v>938571.690760862</v>
+      </c>
+      <c r="G84" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H84" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I84" s="49" t="n">
+        <f aca="false">(I83+Projection!J82)*(1+G84)</f>
+        <v>470166.852858207</v>
+      </c>
+      <c r="J84" s="49" t="n">
+        <f aca="false">I84/PRODUCT(1+H$7:H84)</f>
+        <v>470166.852858207</v>
+      </c>
+      <c r="K84" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L84" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M84" s="49" t="n">
+        <f aca="false">(M83+Projection!J82)*(1+K84)</f>
+        <v>984186.357451944</v>
+      </c>
+      <c r="N84" s="49" t="n">
+        <f aca="false">M84/PRODUCT(1+L$7:L84)</f>
+        <v>984186.357451944</v>
+      </c>
+      <c r="O84" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P84" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q84" s="49" t="n">
+        <f aca="false">(Q83+Projection!J82)*(1+O84)</f>
+        <v>496054.427060926</v>
+      </c>
+      <c r="R84" s="49" t="n">
+        <f aca="false">Q84/PRODUCT(1+P$7:P84)</f>
+        <v>496054.427060926</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="47" t="n">
+        <v>78</v>
+      </c>
+      <c r="B85" s="47" t="n">
+        <v>78</v>
+      </c>
+      <c r="C85" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D85" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E85" s="49" t="n">
+        <f aca="false">(E84+Projection!J83)*(1+C85)</f>
+        <v>1000337.886821</v>
+      </c>
+      <c r="F85" s="49" t="n">
+        <f aca="false">E85/(1+Inputs!B13)^(78+1)</f>
+        <v>1000337.886821</v>
+      </c>
+      <c r="G85" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H85" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I85" s="49" t="n">
+        <f aca="false">(I84+Projection!J83)*(1+G85)</f>
+        <v>501486.73445467</v>
+      </c>
+      <c r="J85" s="49" t="n">
+        <f aca="false">I85/PRODUCT(1+H$7:H85)</f>
+        <v>501486.73445467</v>
+      </c>
+      <c r="K85" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L85" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M85" s="49" t="n">
+        <f aca="false">(M84+Projection!J83)*(1+K85)</f>
+        <v>1048917.506847</v>
+      </c>
+      <c r="N85" s="49" t="n">
+        <f aca="false">M85/PRODUCT(1+L$7:L85)</f>
+        <v>1048917.506847</v>
+      </c>
+      <c r="O85" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P85" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q85" s="49" t="n">
+        <f aca="false">(Q84+Projection!J83)*(1+O85)</f>
+        <v>529057.000980565</v>
+      </c>
+      <c r="R85" s="49" t="n">
+        <f aca="false">Q85/PRODUCT(1+P$7:P85)</f>
+        <v>529057.000980565</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="47" t="n">
+        <v>79</v>
+      </c>
+      <c r="B86" s="47" t="n">
+        <v>79</v>
+      </c>
+      <c r="C86" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D86" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E86" s="49" t="n">
+        <f aca="false">(E85+Projection!J84)*(1+C86)</f>
+        <v>1066130.21452296</v>
+      </c>
+      <c r="F86" s="49" t="n">
+        <f aca="false">E86/(1+Inputs!B13)^(79+1)</f>
+        <v>1066130.21452296</v>
+      </c>
+      <c r="G86" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H86" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I86" s="49" t="n">
+        <f aca="false">(I85+Projection!J84)*(1+G86)</f>
+        <v>534853.737252823</v>
+      </c>
+      <c r="J86" s="49" t="n">
+        <f aca="false">I86/PRODUCT(1+H$7:H86)</f>
+        <v>534853.737252823</v>
+      </c>
+      <c r="K86" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L86" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M86" s="49" t="n">
+        <f aca="false">(M85+Projection!J84)*(1+K86)</f>
+        <v>1117867.50985065</v>
+      </c>
+      <c r="N86" s="49" t="n">
+        <f aca="false">M86/PRODUCT(1+L$7:L86)</f>
+        <v>1117867.50985065</v>
+      </c>
+      <c r="O86" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P86" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q86" s="49" t="n">
+        <f aca="false">(Q85+Projection!J84)*(1+O86)</f>
+        <v>564216.071102902</v>
+      </c>
+      <c r="R86" s="49" t="n">
+        <f aca="false">Q86/PRODUCT(1+P$7:P86)</f>
+        <v>564216.071102902</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="47" t="n">
+        <v>80</v>
+      </c>
+      <c r="B87" s="47" t="n">
+        <v>80</v>
+      </c>
+      <c r="C87" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="D87" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="E87" s="49" t="n">
+        <f aca="false">(E86+Projection!J85)*(1+C87)</f>
+        <v>1136210.5415115</v>
+      </c>
+      <c r="F87" s="49" t="n">
+        <f aca="false">E87/(1+Inputs!B13)^(80+1)</f>
+        <v>1136210.5415115</v>
+      </c>
+      <c r="G87" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="H87" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="I87" s="49" t="n">
+        <f aca="false">(I86+Projection!J85)*(1+G87)</f>
+        <v>570401.093218806</v>
+      </c>
+      <c r="J87" s="49" t="n">
+        <f aca="false">I87/PRODUCT(1+H$7:H87)</f>
+        <v>570401.093218806</v>
+      </c>
+      <c r="K87" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="L87" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="M87" s="49" t="n">
+        <f aca="false">(M86+Projection!J85)*(1+K87)</f>
+        <v>1191310.7610355</v>
+      </c>
+      <c r="N87" s="49" t="n">
+        <f aca="false">M87/PRODUCT(1+L$7:L87)</f>
+        <v>1191310.7610355</v>
+      </c>
+      <c r="O87" s="48" t="n">
+        <f aca="false">Inputs!B14</f>
+        <v>0.065</v>
+      </c>
+      <c r="P87" s="48" t="n">
+        <f aca="false">Inputs!B13</f>
+        <v>0</v>
+      </c>
+      <c r="Q87" s="49" t="n">
+        <f aca="false">(Q86+Projection!J85)*(1+O87)</f>
+        <v>601671.978769139</v>
+      </c>
+      <c r="R87" s="49" t="n">
+        <f aca="false">Q87/PRODUCT(1+P$7:P87)</f>
+        <v>601671.978769139</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="42" t="s">
+        <v>172</v>
+      </c>
+      <c r="B89" s="42"/>
+      <c r="C89" s="42"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="42"/>
+      <c r="G89" s="42"/>
+      <c r="H89" s="42"/>
+      <c r="I89" s="42"/>
+      <c r="J89" s="42"/>
+      <c r="K89" s="42"/>
+      <c r="L89" s="42"/>
+      <c r="M89" s="42"/>
+      <c r="N89" s="42"/>
+      <c r="O89" s="42"/>
+      <c r="P89" s="42"/>
+      <c r="Q89" s="42"/>
+      <c r="R89" s="42"/>
+    </row>
+    <row r="90" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B90" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C90" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="D90" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="E90" s="30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="B91" s="52" t="n">
+        <f aca="false">INDEX(F7:F87,MATCH(Inputs!B20,A7:A87,0))</f>
+        <v>435261.295526382</v>
+      </c>
+      <c r="C91" s="52" t="n">
+        <f aca="false">B91*Inputs!B21</f>
+        <v>17410.4518210553</v>
+      </c>
+      <c r="D91" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="E91" s="53" t="n">
+        <f aca="false">B91/87571</f>
+        <v>4.97038169629652</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="B92" s="54" t="n">
+        <f aca="false">INDEX(J7:J87,MATCH(Inputs!B20,A7:A87,0))</f>
+        <v>215259.574250165</v>
+      </c>
+      <c r="C92" s="54" t="n">
+        <f aca="false">B92*Inputs!B21</f>
+        <v>8610.38297000662</v>
+      </c>
+      <c r="D92" s="55" t="n">
+        <f aca="false">(B92-B91)/B91</f>
+        <v>-0.505447471524336</v>
+      </c>
+      <c r="E92" s="53" t="n">
+        <f aca="false">B92/87571</f>
+        <v>2.4581148353926</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="B93" s="54" t="n">
+        <f aca="false">INDEX(N7:N87,MATCH(Inputs!B20,A7:A87,0))</f>
+        <v>456685.7223799</v>
+      </c>
+      <c r="C93" s="54" t="n">
+        <f aca="false">B93*Inputs!B21</f>
+        <v>18267.428895196</v>
+      </c>
+      <c r="D93" s="55" t="n">
+        <f aca="false">(B93-B91)/B91</f>
+        <v>0.0492219893514943</v>
+      </c>
+      <c r="E93" s="53" t="n">
+        <f aca="false">B93/87571</f>
+        <v>5.21503377122449</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="B94" s="54" t="n">
+        <f aca="false">INDEX(R7:R87,MATCH(Inputs!B20,A7:A87,0))</f>
+        <v>227418.523994932</v>
+      </c>
+      <c r="C94" s="54" t="n">
+        <f aca="false">B94*Inputs!B21</f>
+        <v>9096.74095979728</v>
+      </c>
+      <c r="D94" s="55" t="n">
+        <f aca="false">(B94-B91)/B91</f>
+        <v>-0.47751264279103</v>
+      </c>
+      <c r="E94" s="53" t="n">
+        <f aca="false">B94/87571</f>
+        <v>2.59696159681781</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="B97" s="42"/>
+      <c r="C97" s="42"/>
+      <c r="D97" s="42"/>
+      <c r="E97" s="42"/>
+      <c r="F97" s="42"/>
+      <c r="G97" s="42"/>
+      <c r="H97" s="42"/>
+      <c r="I97" s="42"/>
+      <c r="J97" s="42"/>
+      <c r="K97" s="42"/>
+      <c r="L97" s="42"/>
+      <c r="M97" s="42"/>
+      <c r="N97" s="42"/>
+      <c r="O97" s="42"/>
+      <c r="P97" s="42"/>
+      <c r="Q97" s="42"/>
+      <c r="R97" s="42"/>
+    </row>
+    <row r="98" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
+      <c r="P99" s="3"/>
+      <c r="Q99" s="3"/>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="3"/>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3"/>
+      <c r="O101" s="3"/>
+      <c r="P101" s="3"/>
+      <c r="Q101" s="3"/>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A4:R4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="A89:R89"/>
+    <mergeCell ref="A97:R97"/>
+    <mergeCell ref="A98:R98"/>
+    <mergeCell ref="A99:R99"/>
+    <mergeCell ref="A100:R100"/>
+    <mergeCell ref="A101:R101"/>
+    <mergeCell ref="A102:R102"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -7634,7 +14011,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7643,16 +14020,16 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="41" t="s">
-        <v>163</v>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="56" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7660,208 +14037,208 @@
         <v>2</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="42" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>169</v>
+      <c r="A5" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5" s="57" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>173</v>
+      <c r="A6" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="58" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42" t="s">
-        <v>174</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>177</v>
+      <c r="A7" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" s="57" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>181</v>
+      <c r="A8" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="E8" s="57" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="B9" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>186</v>
+      <c r="A9" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>210</v>
+      </c>
+      <c r="D9" s="58" t="s">
+        <v>211</v>
+      </c>
+      <c r="E9" s="57" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
-        <v>187</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" s="42" t="s">
-        <v>191</v>
+      <c r="A10" s="57" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="E11" s="42" t="s">
-        <v>195</v>
+      <c r="A11" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="D11" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="E11" s="57" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42" t="s">
-        <v>196</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="E12" s="42" t="s">
-        <v>200</v>
+      <c r="A12" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" s="58" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" s="58" t="s">
+        <v>225</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="s">
-        <v>201</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="42" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44" t="s">
-        <v>204</v>
-      </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
+      <c r="A13" s="57" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="57" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="s">
-        <v>205</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
+      <c r="A16" s="59" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" s="60" t="s">
+        <v>232</v>
+      </c>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
     </row>
     <row r="17" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B17" s="46" t="s">
-        <v>208</v>
-      </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
+      <c r="A17" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="B17" s="60" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
     </row>
     <row r="18" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="B18" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
+      <c r="A18" s="59" t="s">
+        <v>235</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>236</v>
+      </c>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -7882,12 +14259,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
@@ -7896,142 +14273,150 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="B3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="47" t="s">
-        <v>213</v>
-      </c>
-      <c r="B4" s="48" t="s">
-        <v>214</v>
+      <c r="A4" s="59" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="47" t="s">
-        <v>215</v>
-      </c>
-      <c r="B5" s="48" t="s">
-        <v>216</v>
+      <c r="A5" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
-        <v>217</v>
-      </c>
-      <c r="B7" s="48" t="s">
-        <v>218</v>
+      <c r="A7" s="59" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="s">
-        <v>219</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>220</v>
+      <c r="A8" s="59" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="61" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="47" t="s">
-        <v>221</v>
-      </c>
-      <c r="B9" s="48" t="s">
-        <v>222</v>
+      <c r="A9" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="47" t="s">
-        <v>223</v>
-      </c>
-      <c r="B11" s="48" t="s">
-        <v>224</v>
+      <c r="A11" s="59" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="B12" s="48" t="s">
-        <v>226</v>
+      <c r="A12" s="59" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="61" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="B13" s="48" t="s">
-        <v>228</v>
+      <c r="A13" s="59" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="47" t="s">
-        <v>229</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>230</v>
+      <c r="A15" s="59" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="47" t="s">
-        <v>231</v>
-      </c>
-      <c r="B16" s="48" t="s">
-        <v>232</v>
+      <c r="A16" s="59" t="s">
+        <v>257</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="B17" s="48" t="s">
-        <v>234</v>
+      <c r="A17" s="59" t="s">
+        <v>259</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="B18" s="48" t="s">
-        <v>236</v>
+      <c r="A18" s="59" t="s">
+        <v>261</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="B20" s="48" t="s">
-        <v>238</v>
+      <c r="A20" s="59" t="s">
+        <v>263</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="B21" s="48" t="s">
-        <v>240</v>
+      <c r="A21" s="59" t="s">
+        <v>265</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="47" t="s">
-        <v>241</v>
-      </c>
-      <c r="B23" s="48" t="s">
-        <v>242</v>
+      <c r="A23" s="59" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="47" t="s">
-        <v>241</v>
-      </c>
-      <c r="B25" s="48" t="s">
-        <v>243</v>
+      <c r="A25" s="59" t="s">
+        <v>267</v>
+      </c>
+      <c r="B25" s="61" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="62" t="s">
+        <v>270</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
